--- a/Configuration_Catalogue.xlsx
+++ b/Configuration_Catalogue.xlsx
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2929" uniqueCount="607">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2933" uniqueCount="608">
   <si>
     <t>HARDWARE LAB | CATALOGUE</t>
   </si>
@@ -484,21 +484,27 @@
     <t>AMD Ryzen 5 1600</t>
   </si>
   <si>
+    <t>DDR4</t>
+  </si>
+  <si>
     <t>AM4</t>
   </si>
   <si>
+    <t>Processeur AMD Ryzen 5 1600 pour PC de bureau, architecture Zen (Summit Ridge, variante AE 14 nm). 6 cœurs physiques et 12 threads grâce au SMT. Jeu d'instructions x86-64, AES pour accélérer les opérations cryptographiques, AVX2 et FMA3 pour les calculs vectoriels, virtualisation matérielle AMD-V. Fréquences 3,2 GHz de base et jusqu'à 3,6 GHz en boost ; cache L3 16 Mo, TDP 65 W. Plateforme AM4 avec mémoire DDR4 double canal et PCIe 3.0. Requiert une carte graphique dédiée. Ne pas confondre avec la variante AF 12 nm. Technologies documentées : x86-64 (64 bits), SMT, AES, AVX2, FMA3, AMD-V (virtualisation), AMD SenseMI, XFR.</t>
+  </si>
+  <si>
+    <t>Assets/CPU/CPU - AMD Ryzen 5 1600.jpg</t>
+  </si>
+  <si>
+    <t>Component/CPU/AMD_Ryzen_5_1600.json</t>
+  </si>
+  <si>
+    <t>AMD Ryzen 5 2600</t>
+  </si>
+  <si>
     <t>CPU 6 cœurs / 12 threads, socket AM4.</t>
   </si>
   <si>
-    <t>Assets/CPU/CPU - AMD Ryzen 5 1600.jpg</t>
-  </si>
-  <si>
-    <t>Component/CPU/AMD_Ryzen_5_1600.json</t>
-  </si>
-  <si>
-    <t>AMD Ryzen 5 2600</t>
-  </si>
-  <si>
     <t>Assets/CPU/CPU - AMD Ryzen 5 2600.jpg</t>
   </si>
   <si>
@@ -1424,9 +1430,6 @@
   </si>
   <si>
     <t>Corsair Vengeance LPX 16GB 2x8 DDR4-3200 CL16</t>
-  </si>
-  <si>
-    <t>DDR4</t>
   </si>
   <si>
     <t>Corsair Vengeance LPX 16GB 2x8 DDR4-3200 CL16 — spécifications partielles</t>
@@ -2639,16 +2642,16 @@
     </row>
     <row r="2" spans="1:18">
       <c r="A2" s="3" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="G2" s="3">
         <v>2000</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="J2" s="3">
         <v>0</v>
@@ -2660,21 +2663,21 @@
         <v>36</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="4" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="G3" s="3">
         <v>1000</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="J3" s="3">
         <v>0</v>
@@ -2686,21 +2689,21 @@
         <v>36</v>
       </c>
       <c r="R3" s="4" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="4" spans="1:18">
       <c r="A4" s="3" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="G4" s="3">
         <v>1000</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="J4" s="3">
         <v>0</v>
@@ -2712,21 +2715,21 @@
         <v>36</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="5" spans="1:18">
       <c r="A5" s="4" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="G5" s="3">
         <v>500</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="J5" s="3">
         <v>0</v>
@@ -2738,21 +2741,21 @@
         <v>36</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="6" spans="1:18">
       <c r="A6" s="3" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="G6" s="3">
         <v>1000</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="J6" s="3">
         <v>0</v>
@@ -2764,21 +2767,21 @@
         <v>36</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="7" spans="1:18">
       <c r="A7" s="4" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="G7" s="3">
         <v>2000</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="J7" s="3">
         <v>0</v>
@@ -2790,21 +2793,21 @@
         <v>36</v>
       </c>
       <c r="R7" s="4" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="8" spans="1:18">
       <c r="A8" s="3" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="G8" s="3">
         <v>1000</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="J8" s="3">
         <v>0</v>
@@ -2816,21 +2819,21 @@
         <v>36</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="4" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="G9" s="3">
         <v>500</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="J9" s="3">
         <v>0</v>
@@ -2842,21 +2845,21 @@
         <v>36</v>
       </c>
       <c r="R9" s="4" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="3" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="G10" s="3">
         <v>1000</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="J10" s="3">
         <v>0</v>
@@ -2868,21 +2871,21 @@
         <v>36</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="11" spans="1:18">
       <c r="A11" s="4" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="G11" s="3">
         <v>1000</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="J11" s="3">
         <v>0</v>
@@ -2894,21 +2897,21 @@
         <v>36</v>
       </c>
       <c r="R11" s="4" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="12" spans="1:18">
       <c r="A12" s="3" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="G12" s="3">
         <v>1000</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="J12" s="3">
         <v>0</v>
@@ -2920,21 +2923,21 @@
         <v>36</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="4" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="G13" s="3">
         <v>1000</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="J13" s="3">
         <v>0</v>
@@ -2946,21 +2949,21 @@
         <v>36</v>
       </c>
       <c r="R13" s="4" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="3" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="G14" s="3">
         <v>2000</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="J14" s="3">
         <v>0</v>
@@ -2972,7 +2975,7 @@
         <v>36</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
   </sheetData>
@@ -3053,13 +3056,13 @@
     </row>
     <row r="2" spans="1:18">
       <c r="A2" s="3" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="G2" s="3">
         <v>900</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="J2" s="3">
         <v>0</v>
@@ -3071,18 +3074,18 @@
         <v>36</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="4" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="G3" s="3">
         <v>2000</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="J3" s="3">
         <v>0</v>
@@ -3094,18 +3097,18 @@
         <v>36</v>
       </c>
       <c r="R3" s="4" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="4" spans="1:18">
       <c r="A4" s="3" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="G4" s="3">
         <v>1200</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="J4" s="3">
         <v>0</v>
@@ -3117,18 +3120,18 @@
         <v>36</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="5" spans="1:18">
       <c r="A5" s="4" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="G5" s="3">
         <v>8000</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="J5" s="3">
         <v>0</v>
@@ -3140,18 +3143,18 @@
         <v>36</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="6" spans="1:18">
       <c r="A6" s="3" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="G6" s="3">
         <v>4000</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="J6" s="3">
         <v>0</v>
@@ -3163,18 +3166,18 @@
         <v>36</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="7" spans="1:18">
       <c r="A7" s="4" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="G7" s="3">
         <v>1000</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="J7" s="3">
         <v>0</v>
@@ -3186,18 +3189,18 @@
         <v>36</v>
       </c>
       <c r="R7" s="4" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="8" spans="1:18">
       <c r="A8" s="3" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="G8" s="3">
         <v>10000</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="J8" s="3">
         <v>0</v>
@@ -3209,18 +3212,18 @@
         <v>36</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="4" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="G9" s="3">
         <v>6000</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="J9" s="3">
         <v>0</v>
@@ -3232,7 +3235,7 @@
         <v>36</v>
       </c>
       <c r="R9" s="4" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
   </sheetData>
@@ -3413,13 +3416,13 @@
         <v>30</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>29</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -4129,7 +4132,7 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B49" t="s">
         <v>4</v>
@@ -4144,7 +4147,7 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B50" t="s">
         <v>4</v>
@@ -4159,7 +4162,7 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B51" t="s">
         <v>4</v>
@@ -4174,7 +4177,7 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B52" t="s">
         <v>4</v>
@@ -4189,7 +4192,7 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B53" t="s">
         <v>4</v>
@@ -4204,7 +4207,7 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B54" t="s">
         <v>4</v>
@@ -4219,13 +4222,13 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B55" t="s">
         <v>4</v>
       </c>
       <c r="C55" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F55" s="5">
         <f>IF(D55="","",D55+IF(E55="",0,E55))</f>
@@ -4234,7 +4237,7 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B56" t="s">
         <v>4</v>
@@ -4249,7 +4252,7 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B57" t="s">
         <v>4</v>
@@ -4264,7 +4267,7 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B58" t="s">
         <v>4</v>
@@ -4279,7 +4282,7 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B59" t="s">
         <v>4</v>
@@ -4294,7 +4297,7 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B60" t="s">
         <v>4</v>
@@ -4309,7 +4312,7 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B61" t="s">
         <v>4</v>
@@ -4324,7 +4327,7 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B62" t="s">
         <v>4</v>
@@ -4339,7 +4342,7 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B63" t="s">
         <v>4</v>
@@ -4354,7 +4357,7 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B64" t="s">
         <v>4</v>
@@ -4369,7 +4372,7 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B65" t="s">
         <v>4</v>
@@ -4384,7 +4387,7 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B66" t="s">
         <v>4</v>
@@ -4399,7 +4402,7 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B67" t="s">
         <v>4</v>
@@ -4414,7 +4417,7 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B68" t="s">
         <v>4</v>
@@ -4429,7 +4432,7 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B69" t="s">
         <v>4</v>
@@ -4444,7 +4447,7 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B70" t="s">
         <v>4</v>
@@ -4459,7 +4462,7 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B71" t="s">
         <v>4</v>
@@ -4474,7 +4477,7 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B72" t="s">
         <v>4</v>
@@ -4489,7 +4492,7 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B73" t="s">
         <v>4</v>
@@ -4504,7 +4507,7 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B74" t="s">
         <v>4</v>
@@ -4519,7 +4522,7 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B75" t="s">
         <v>4</v>
@@ -4534,7 +4537,7 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B76" t="s">
         <v>4</v>
@@ -4549,7 +4552,7 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B77" t="s">
         <v>4</v>
@@ -4564,7 +4567,7 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B78" t="s">
         <v>4</v>
@@ -4579,7 +4582,7 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B79" t="s">
         <v>4</v>
@@ -4594,7 +4597,7 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B80" t="s">
         <v>4</v>
@@ -4609,7 +4612,7 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B81" t="s">
         <v>4</v>
@@ -4624,7 +4627,7 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B82" t="s">
         <v>5</v>
@@ -4639,7 +4642,7 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B83" t="s">
         <v>5</v>
@@ -4654,7 +4657,7 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B84" t="s">
         <v>5</v>
@@ -4669,7 +4672,7 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B85" t="s">
         <v>5</v>
@@ -4684,7 +4687,7 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B86" t="s">
         <v>5</v>
@@ -4699,7 +4702,7 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B87" t="s">
         <v>5</v>
@@ -4714,7 +4717,7 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B88" t="s">
         <v>5</v>
@@ -4729,7 +4732,7 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B89" t="s">
         <v>5</v>
@@ -4744,7 +4747,7 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B90" t="s">
         <v>5</v>
@@ -4759,7 +4762,7 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B91" t="s">
         <v>5</v>
@@ -4774,7 +4777,7 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B92" t="s">
         <v>5</v>
@@ -4789,7 +4792,7 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B93" t="s">
         <v>5</v>
@@ -4804,7 +4807,7 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B94" t="s">
         <v>5</v>
@@ -4819,7 +4822,7 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B95" t="s">
         <v>5</v>
@@ -4834,7 +4837,7 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B96" t="s">
         <v>5</v>
@@ -4849,13 +4852,13 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B97" t="s">
         <v>5</v>
       </c>
       <c r="C97" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F97" s="5">
         <f>IF(D97="","",D97+IF(E97="",0,E97))</f>
@@ -4864,7 +4867,7 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B98" t="s">
         <v>5</v>
@@ -4879,7 +4882,7 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B99" t="s">
         <v>5</v>
@@ -4894,7 +4897,7 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B100" t="s">
         <v>5</v>
@@ -4909,7 +4912,7 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B101" t="s">
         <v>5</v>
@@ -4924,7 +4927,7 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B102" t="s">
         <v>5</v>
@@ -4939,7 +4942,7 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B103" t="s">
         <v>5</v>
@@ -4954,7 +4957,7 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B104" t="s">
         <v>5</v>
@@ -4969,7 +4972,7 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B105" t="s">
         <v>5</v>
@@ -4984,7 +4987,7 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B106" t="s">
         <v>5</v>
@@ -4999,7 +5002,7 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B107" t="s">
         <v>5</v>
@@ -5014,7 +5017,7 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B108" t="s">
         <v>5</v>
@@ -5029,7 +5032,7 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B109" t="s">
         <v>5</v>
@@ -5044,7 +5047,7 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B110" t="s">
         <v>5</v>
@@ -5059,7 +5062,7 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B111" t="s">
         <v>5</v>
@@ -5074,7 +5077,7 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B112" t="s">
         <v>5</v>
@@ -5089,13 +5092,13 @@
     </row>
     <row r="113" spans="1:6">
       <c r="A113" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B113" t="s">
         <v>6</v>
       </c>
       <c r="C113" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F113" s="5">
         <f>IF(D113="","",D113+IF(E113="",0,E113))</f>
@@ -5104,7 +5107,7 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B114" t="s">
         <v>6</v>
@@ -5119,7 +5122,7 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B115" t="s">
         <v>6</v>
@@ -5134,7 +5137,7 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B116" t="s">
         <v>6</v>
@@ -5149,7 +5152,7 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B117" t="s">
         <v>6</v>
@@ -5164,7 +5167,7 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B118" t="s">
         <v>6</v>
@@ -5179,7 +5182,7 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B119" t="s">
         <v>6</v>
@@ -5194,7 +5197,7 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B120" t="s">
         <v>6</v>
@@ -5209,7 +5212,7 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B121" t="s">
         <v>6</v>
@@ -5224,7 +5227,7 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B122" t="s">
         <v>6</v>
@@ -5239,7 +5242,7 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B123" t="s">
         <v>6</v>
@@ -5254,7 +5257,7 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B124" t="s">
         <v>6</v>
@@ -5269,7 +5272,7 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B125" t="s">
         <v>6</v>
@@ -5284,7 +5287,7 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B126" t="s">
         <v>6</v>
@@ -5299,7 +5302,7 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B127" t="s">
         <v>6</v>
@@ -5314,13 +5317,13 @@
     </row>
     <row r="128" spans="1:6">
       <c r="A128" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B128" t="s">
         <v>7</v>
       </c>
       <c r="C128" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F128" s="5">
         <f>IF(D128="","",D128+IF(E128="",0,E128))</f>
@@ -5329,7 +5332,7 @@
     </row>
     <row r="129" spans="1:6">
       <c r="A129" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B129" t="s">
         <v>7</v>
@@ -5344,7 +5347,7 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B130" t="s">
         <v>7</v>
@@ -5359,7 +5362,7 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B131" t="s">
         <v>7</v>
@@ -5374,7 +5377,7 @@
     </row>
     <row r="132" spans="1:6">
       <c r="A132" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B132" t="s">
         <v>7</v>
@@ -5389,7 +5392,7 @@
     </row>
     <row r="133" spans="1:6">
       <c r="A133" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B133" t="s">
         <v>7</v>
@@ -5404,7 +5407,7 @@
     </row>
     <row r="134" spans="1:6">
       <c r="A134" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B134" t="s">
         <v>7</v>
@@ -5419,7 +5422,7 @@
     </row>
     <row r="135" spans="1:6">
       <c r="A135" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B135" t="s">
         <v>7</v>
@@ -5434,7 +5437,7 @@
     </row>
     <row r="136" spans="1:6">
       <c r="A136" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B136" t="s">
         <v>7</v>
@@ -5449,7 +5452,7 @@
     </row>
     <row r="137" spans="1:6">
       <c r="A137" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B137" t="s">
         <v>7</v>
@@ -5464,7 +5467,7 @@
     </row>
     <row r="138" spans="1:6">
       <c r="A138" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B138" t="s">
         <v>7</v>
@@ -5479,7 +5482,7 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B139" t="s">
         <v>7</v>
@@ -5494,7 +5497,7 @@
     </row>
     <row r="140" spans="1:6">
       <c r="A140" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B140" t="s">
         <v>7</v>
@@ -5509,7 +5512,7 @@
     </row>
     <row r="141" spans="1:6">
       <c r="A141" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B141" t="s">
         <v>7</v>
@@ -5524,7 +5527,7 @@
     </row>
     <row r="142" spans="1:6">
       <c r="A142" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B142" t="s">
         <v>7</v>
@@ -5539,7 +5542,7 @@
     </row>
     <row r="143" spans="1:6">
       <c r="A143" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B143" t="s">
         <v>7</v>
@@ -5554,7 +5557,7 @@
     </row>
     <row r="144" spans="1:6">
       <c r="A144" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B144" t="s">
         <v>7</v>
@@ -5569,7 +5572,7 @@
     </row>
     <row r="145" spans="1:6">
       <c r="A145" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B145" t="s">
         <v>7</v>
@@ -5584,7 +5587,7 @@
     </row>
     <row r="146" spans="1:6">
       <c r="A146" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B146" t="s">
         <v>7</v>
@@ -5599,7 +5602,7 @@
     </row>
     <row r="147" spans="1:6">
       <c r="A147" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B147" t="s">
         <v>8</v>
@@ -5614,7 +5617,7 @@
     </row>
     <row r="148" spans="1:6">
       <c r="A148" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B148" t="s">
         <v>8</v>
@@ -5629,7 +5632,7 @@
     </row>
     <row r="149" spans="1:6">
       <c r="A149" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B149" t="s">
         <v>8</v>
@@ -5644,7 +5647,7 @@
     </row>
     <row r="150" spans="1:6">
       <c r="A150" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B150" t="s">
         <v>8</v>
@@ -5659,7 +5662,7 @@
     </row>
     <row r="151" spans="1:6">
       <c r="A151" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B151" t="s">
         <v>8</v>
@@ -5674,7 +5677,7 @@
     </row>
     <row r="152" spans="1:6">
       <c r="A152" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B152" t="s">
         <v>8</v>
@@ -5689,7 +5692,7 @@
     </row>
     <row r="153" spans="1:6">
       <c r="A153" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B153" t="s">
         <v>8</v>
@@ -5704,7 +5707,7 @@
     </row>
     <row r="154" spans="1:6">
       <c r="A154" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B154" t="s">
         <v>8</v>
@@ -5719,7 +5722,7 @@
     </row>
     <row r="155" spans="1:6">
       <c r="A155" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B155" t="s">
         <v>8</v>
@@ -5734,7 +5737,7 @@
     </row>
     <row r="156" spans="1:6">
       <c r="A156" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B156" t="s">
         <v>9</v>
@@ -5749,7 +5752,7 @@
     </row>
     <row r="157" spans="1:6">
       <c r="A157" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B157" t="s">
         <v>9</v>
@@ -5764,7 +5767,7 @@
     </row>
     <row r="158" spans="1:6">
       <c r="A158" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B158" t="s">
         <v>9</v>
@@ -5779,7 +5782,7 @@
     </row>
     <row r="159" spans="1:6">
       <c r="A159" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B159" t="s">
         <v>9</v>
@@ -5794,7 +5797,7 @@
     </row>
     <row r="160" spans="1:6">
       <c r="A160" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B160" t="s">
         <v>9</v>
@@ -5809,7 +5812,7 @@
     </row>
     <row r="161" spans="1:6">
       <c r="A161" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B161" t="s">
         <v>9</v>
@@ -5824,7 +5827,7 @@
     </row>
     <row r="162" spans="1:6">
       <c r="A162" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B162" t="s">
         <v>9</v>
@@ -5839,7 +5842,7 @@
     </row>
     <row r="163" spans="1:6">
       <c r="A163" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B163" t="s">
         <v>9</v>
@@ -5854,7 +5857,7 @@
     </row>
     <row r="164" spans="1:6">
       <c r="A164" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B164" t="s">
         <v>9</v>
@@ -5869,7 +5872,7 @@
     </row>
     <row r="165" spans="1:6">
       <c r="A165" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B165" t="s">
         <v>9</v>
@@ -5884,7 +5887,7 @@
     </row>
     <row r="166" spans="1:6">
       <c r="A166" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B166" t="s">
         <v>9</v>
@@ -5899,7 +5902,7 @@
     </row>
     <row r="167" spans="1:6">
       <c r="A167" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B167" t="s">
         <v>10</v>
@@ -5914,7 +5917,7 @@
     </row>
     <row r="168" spans="1:6">
       <c r="A168" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B168" t="s">
         <v>10</v>
@@ -5929,7 +5932,7 @@
     </row>
     <row r="169" spans="1:6">
       <c r="A169" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B169" t="s">
         <v>10</v>
@@ -5944,7 +5947,7 @@
     </row>
     <row r="170" spans="1:6">
       <c r="A170" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B170" t="s">
         <v>10</v>
@@ -5959,7 +5962,7 @@
     </row>
     <row r="171" spans="1:6">
       <c r="A171" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B171" t="s">
         <v>10</v>
@@ -5974,7 +5977,7 @@
     </row>
     <row r="172" spans="1:6">
       <c r="A172" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B172" t="s">
         <v>10</v>
@@ -5989,7 +5992,7 @@
     </row>
     <row r="173" spans="1:6">
       <c r="A173" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B173" t="s">
         <v>10</v>
@@ -6004,7 +6007,7 @@
     </row>
     <row r="174" spans="1:6">
       <c r="A174" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B174" t="s">
         <v>10</v>
@@ -6019,7 +6022,7 @@
     </row>
     <row r="175" spans="1:6">
       <c r="A175" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B175" t="s">
         <v>10</v>
@@ -6034,7 +6037,7 @@
     </row>
     <row r="176" spans="1:6">
       <c r="A176" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B176" t="s">
         <v>10</v>
@@ -6049,7 +6052,7 @@
     </row>
     <row r="177" spans="1:6">
       <c r="A177" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B177" t="s">
         <v>10</v>
@@ -6064,7 +6067,7 @@
     </row>
     <row r="178" spans="1:6">
       <c r="A178" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B178" t="s">
         <v>10</v>
@@ -6079,7 +6082,7 @@
     </row>
     <row r="179" spans="1:6">
       <c r="A179" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B179" t="s">
         <v>10</v>
@@ -6094,7 +6097,7 @@
     </row>
     <row r="180" spans="1:6">
       <c r="A180" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B180" t="s">
         <v>11</v>
@@ -6109,7 +6112,7 @@
     </row>
     <row r="181" spans="1:6">
       <c r="A181" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B181" t="s">
         <v>11</v>
@@ -6124,7 +6127,7 @@
     </row>
     <row r="182" spans="1:6">
       <c r="A182" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B182" t="s">
         <v>11</v>
@@ -6139,7 +6142,7 @@
     </row>
     <row r="183" spans="1:6">
       <c r="A183" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B183" t="s">
         <v>11</v>
@@ -6154,7 +6157,7 @@
     </row>
     <row r="184" spans="1:6">
       <c r="A184" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B184" t="s">
         <v>11</v>
@@ -6169,7 +6172,7 @@
     </row>
     <row r="185" spans="1:6">
       <c r="A185" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B185" t="s">
         <v>11</v>
@@ -6184,7 +6187,7 @@
     </row>
     <row r="186" spans="1:6">
       <c r="A186" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B186" t="s">
         <v>11</v>
@@ -6199,7 +6202,7 @@
     </row>
     <row r="187" spans="1:6">
       <c r="A187" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B187" t="s">
         <v>11</v>
@@ -6229,15 +6232,15 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B2" s="5">
         <f>SUM(INVENTAIRE!D2:D187)</f>
@@ -6246,7 +6249,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B3" s="5">
         <f>SUMIF(INVENTAIRE!D2:D187,"&gt;=0",INVENTAIRE!E2:E187)</f>
@@ -6255,7 +6258,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B4" s="5">
         <f>B2+B3</f>
@@ -6278,50 +6281,50 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B2" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B3" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B4" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B5" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B6" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -6329,15 +6332,15 @@
         <v>31</v>
       </c>
       <c r="B7" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B8" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
   </sheetData>
@@ -7628,6 +7631,9 @@
       <c r="B48" s="3" t="s">
         <v>145</v>
       </c>
+      <c r="D48" s="3" t="s">
+        <v>146</v>
+      </c>
       <c r="E48" s="3">
         <v>6</v>
       </c>
@@ -7635,10 +7641,10 @@
         <v>12</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K48" s="3">
         <v>0</v>
@@ -7650,10 +7656,13 @@
         <v>36</v>
       </c>
       <c r="Q48" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
+      </c>
+      <c r="R48" s="3" t="s">
+        <v>93</v>
       </c>
       <c r="S48" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="49" spans="1:19">
@@ -7661,7 +7670,7 @@
         <v>4</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E49" s="3">
         <v>6</v>
@@ -7670,10 +7679,10 @@
         <v>12</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="K49" s="3">
         <v>0</v>
@@ -7685,10 +7694,10 @@
         <v>36</v>
       </c>
       <c r="Q49" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="S49" s="4" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="50" spans="1:19">
@@ -7696,7 +7705,7 @@
         <v>4</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E50" s="3">
         <v>6</v>
@@ -7705,10 +7714,10 @@
         <v>12</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="K50" s="3">
         <v>0</v>
@@ -7720,10 +7729,10 @@
         <v>36</v>
       </c>
       <c r="Q50" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="S50" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="51" spans="1:19">
@@ -7731,7 +7740,7 @@
         <v>4</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E51" s="3">
         <v>6</v>
@@ -7740,10 +7749,10 @@
         <v>12</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I51" s="4" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="K51" s="3">
         <v>0</v>
@@ -7755,10 +7764,10 @@
         <v>36</v>
       </c>
       <c r="Q51" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="S51" s="4" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="52" spans="1:19">
@@ -7766,7 +7775,7 @@
         <v>4</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E52" s="3">
         <v>6</v>
@@ -7775,10 +7784,10 @@
         <v>12</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -7790,10 +7799,10 @@
         <v>36</v>
       </c>
       <c r="Q52" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="S52" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="53" spans="1:19">
@@ -7801,7 +7810,7 @@
         <v>4</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E53" s="3">
         <v>6</v>
@@ -7810,10 +7819,10 @@
         <v>12</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="I53" s="4" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="K53" s="3">
         <v>0</v>
@@ -7825,10 +7834,10 @@
         <v>36</v>
       </c>
       <c r="Q53" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="S53" s="4" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="54" spans="1:19">
@@ -7836,7 +7845,7 @@
         <v>4</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E54" s="3">
         <v>6</v>
@@ -7845,10 +7854,10 @@
         <v>12</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="K54" s="3">
         <v>0</v>
@@ -7860,7 +7869,7 @@
         <v>36</v>
       </c>
       <c r="S54" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="55" spans="1:19">
@@ -7868,7 +7877,7 @@
         <v>4</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E55" s="3">
         <v>8</v>
@@ -7877,10 +7886,10 @@
         <v>16</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I55" s="4" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="K55" s="3">
         <v>0</v>
@@ -7889,10 +7898,10 @@
         <v>0</v>
       </c>
       <c r="P55" s="4" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="S55" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="56" spans="1:19">
@@ -7900,7 +7909,7 @@
         <v>4</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E56" s="3">
         <v>8</v>
@@ -7909,10 +7918,10 @@
         <v>16</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="K56" s="3">
         <v>0</v>
@@ -7924,7 +7933,7 @@
         <v>36</v>
       </c>
       <c r="S56" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="57" spans="1:19">
@@ -7932,7 +7941,7 @@
         <v>4</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E57" s="3">
         <v>8</v>
@@ -7941,10 +7950,10 @@
         <v>16</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I57" s="4" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="K57" s="3">
         <v>0</v>
@@ -7956,7 +7965,7 @@
         <v>36</v>
       </c>
       <c r="S57" s="4" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="58" spans="1:19">
@@ -7964,7 +7973,7 @@
         <v>4</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E58" s="3">
         <v>8</v>
@@ -7973,10 +7982,10 @@
         <v>16</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -7988,7 +7997,7 @@
         <v>36</v>
       </c>
       <c r="S58" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="59" spans="1:19">
@@ -7996,7 +8005,7 @@
         <v>4</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E59" s="3">
         <v>8</v>
@@ -8005,10 +8014,10 @@
         <v>16</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I59" s="4" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="K59" s="3">
         <v>0</v>
@@ -8020,7 +8029,7 @@
         <v>36</v>
       </c>
       <c r="S59" s="4" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="60" spans="1:19">
@@ -8028,7 +8037,7 @@
         <v>4</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E60" s="3">
         <v>8</v>
@@ -8037,10 +8046,10 @@
         <v>16</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -8052,7 +8061,7 @@
         <v>36</v>
       </c>
       <c r="S60" s="3" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="61" spans="1:19">
@@ -8060,7 +8069,7 @@
         <v>4</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E61" s="3">
         <v>8</v>
@@ -8069,10 +8078,10 @@
         <v>16</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="I61" s="4" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -8084,7 +8093,7 @@
         <v>36</v>
       </c>
       <c r="S61" s="4" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="62" spans="1:19">
@@ -8092,7 +8101,7 @@
         <v>4</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E62" s="3">
         <v>8</v>
@@ -8101,10 +8110,10 @@
         <v>16</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -8116,7 +8125,7 @@
         <v>36</v>
       </c>
       <c r="S62" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="63" spans="1:19">
@@ -8124,7 +8133,7 @@
         <v>4</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E63" s="3">
         <v>8</v>
@@ -8133,10 +8142,10 @@
         <v>16</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="I63" s="4" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="K63" s="3">
         <v>0</v>
@@ -8148,7 +8157,7 @@
         <v>36</v>
       </c>
       <c r="S63" s="4" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="64" spans="1:19">
@@ -8156,7 +8165,7 @@
         <v>4</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E64" s="3">
         <v>12</v>
@@ -8165,10 +8174,10 @@
         <v>24</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="K64" s="3">
         <v>0</v>
@@ -8180,7 +8189,7 @@
         <v>36</v>
       </c>
       <c r="S64" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="65" spans="1:19">
@@ -8188,7 +8197,7 @@
         <v>4</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E65" s="3">
         <v>16</v>
@@ -8197,10 +8206,10 @@
         <v>32</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I65" s="4" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="K65" s="3">
         <v>0</v>
@@ -8212,7 +8221,7 @@
         <v>36</v>
       </c>
       <c r="S65" s="4" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="66" spans="1:19">
@@ -8220,7 +8229,7 @@
         <v>4</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E66" s="3">
         <v>16</v>
@@ -8229,10 +8238,10 @@
         <v>32</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="K66" s="3">
         <v>0</v>
@@ -8244,7 +8253,7 @@
         <v>36</v>
       </c>
       <c r="S66" s="3" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="67" spans="1:19">
@@ -8252,7 +8261,7 @@
         <v>4</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E67" s="3">
         <v>6</v>
@@ -8261,10 +8270,10 @@
         <v>12</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="I67" s="4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="K67" s="3">
         <v>0</v>
@@ -8276,7 +8285,7 @@
         <v>36</v>
       </c>
       <c r="S67" s="4" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="68" spans="1:19">
@@ -8284,7 +8293,7 @@
         <v>4</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E68" s="3">
         <v>6</v>
@@ -8293,10 +8302,10 @@
         <v>12</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="K68" s="3">
         <v>0</v>
@@ -8308,7 +8317,7 @@
         <v>36</v>
       </c>
       <c r="S68" s="3" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="69" spans="1:19">
@@ -8316,7 +8325,7 @@
         <v>4</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E69" s="3">
         <v>6</v>
@@ -8325,10 +8334,10 @@
         <v>12</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I69" s="4" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="K69" s="3">
         <v>0</v>
@@ -8340,7 +8349,7 @@
         <v>36</v>
       </c>
       <c r="S69" s="4" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="70" spans="1:19">
@@ -8348,7 +8357,7 @@
         <v>4</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E70" s="3">
         <v>10</v>
@@ -8357,10 +8366,10 @@
         <v>16</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="K70" s="3">
         <v>0</v>
@@ -8372,7 +8381,7 @@
         <v>36</v>
       </c>
       <c r="S70" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="71" spans="1:19">
@@ -8380,7 +8389,7 @@
         <v>4</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E71" s="3">
         <v>14</v>
@@ -8389,10 +8398,10 @@
         <v>20</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I71" s="4" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="K71" s="3">
         <v>0</v>
@@ -8404,7 +8413,7 @@
         <v>36</v>
       </c>
       <c r="S71" s="4" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="72" spans="1:19">
@@ -8412,7 +8421,7 @@
         <v>4</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E72" s="3">
         <v>14</v>
@@ -8421,10 +8430,10 @@
         <v>20</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="K72" s="3">
         <v>0</v>
@@ -8436,7 +8445,7 @@
         <v>36</v>
       </c>
       <c r="S72" s="3" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="73" spans="1:19">
@@ -8444,7 +8453,7 @@
         <v>4</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E73" s="3">
         <v>8</v>
@@ -8453,10 +8462,10 @@
         <v>16</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="I73" s="4" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="K73" s="3">
         <v>0</v>
@@ -8468,7 +8477,7 @@
         <v>36</v>
       </c>
       <c r="S73" s="4" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="74" spans="1:19">
@@ -8476,7 +8485,7 @@
         <v>4</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E74" s="3">
         <v>12</v>
@@ -8485,10 +8494,10 @@
         <v>20</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="K74" s="3">
         <v>0</v>
@@ -8500,7 +8509,7 @@
         <v>36</v>
       </c>
       <c r="S74" s="3" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="75" spans="1:19">
@@ -8508,7 +8517,7 @@
         <v>4</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="E75" s="3">
         <v>16</v>
@@ -8517,10 +8526,10 @@
         <v>24</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I75" s="4" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="K75" s="3">
         <v>0</v>
@@ -8532,7 +8541,7 @@
         <v>36</v>
       </c>
       <c r="S75" s="4" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="76" spans="1:19">
@@ -8540,7 +8549,7 @@
         <v>4</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E76" s="3">
         <v>20</v>
@@ -8549,10 +8558,10 @@
         <v>28</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="K76" s="3">
         <v>0</v>
@@ -8564,7 +8573,7 @@
         <v>36</v>
       </c>
       <c r="S76" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="77" spans="1:19">
@@ -8572,7 +8581,7 @@
         <v>4</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E77" s="3">
         <v>4</v>
@@ -8581,10 +8590,10 @@
         <v>8</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="I77" s="4" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="K77" s="3">
         <v>0</v>
@@ -8596,7 +8605,7 @@
         <v>36</v>
       </c>
       <c r="S77" s="4" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="78" spans="1:19">
@@ -8604,7 +8613,7 @@
         <v>4</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E78" s="3">
         <v>4</v>
@@ -8613,10 +8622,10 @@
         <v>8</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="K78" s="3">
         <v>0</v>
@@ -8628,7 +8637,7 @@
         <v>36</v>
       </c>
       <c r="S78" s="3" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="79" spans="1:19">
@@ -8636,7 +8645,7 @@
         <v>4</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E79" s="3">
         <v>4</v>
@@ -8645,10 +8654,10 @@
         <v>8</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I79" s="4" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="K79" s="3">
         <v>0</v>
@@ -8660,7 +8669,7 @@
         <v>36</v>
       </c>
       <c r="S79" s="4" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="80" spans="1:19">
@@ -8668,7 +8677,7 @@
         <v>4</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E80" s="3">
         <v>6</v>
@@ -8677,10 +8686,10 @@
         <v>12</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="K80" s="3">
         <v>0</v>
@@ -8692,7 +8701,7 @@
         <v>36</v>
       </c>
       <c r="S80" s="3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="81" spans="1:19">
@@ -8700,7 +8709,7 @@
         <v>4</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E81" s="3">
         <v>8</v>
@@ -8709,10 +8718,10 @@
         <v>8</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I81" s="4" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="K81" s="3">
         <v>0</v>
@@ -8724,7 +8733,7 @@
         <v>36</v>
       </c>
       <c r="S81" s="4" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="82" spans="1:19">
@@ -8732,19 +8741,19 @@
         <v>5</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="K82" s="3">
         <v>0</v>
@@ -8756,7 +8765,7 @@
         <v>36</v>
       </c>
       <c r="S82" s="3" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="83" spans="1:19">
@@ -8764,19 +8773,19 @@
         <v>5</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I83" s="4" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -8788,7 +8797,7 @@
         <v>36</v>
       </c>
       <c r="S83" s="4" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="84" spans="1:19">
@@ -8796,19 +8805,19 @@
         <v>5</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="K84" s="3">
         <v>0</v>
@@ -8820,7 +8829,7 @@
         <v>36</v>
       </c>
       <c r="S84" s="3" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="85" spans="1:19">
@@ -8828,19 +8837,19 @@
         <v>5</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I85" s="4" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K85" s="3">
         <v>0</v>
@@ -8852,7 +8861,7 @@
         <v>36</v>
       </c>
       <c r="S85" s="4" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="86" spans="1:19">
@@ -8860,19 +8869,19 @@
         <v>5</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="K86" s="3">
         <v>0</v>
@@ -8884,7 +8893,7 @@
         <v>36</v>
       </c>
       <c r="S86" s="3" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="87" spans="1:19">
@@ -8892,19 +8901,19 @@
         <v>5</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="I87" s="4" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="K87" s="3">
         <v>0</v>
@@ -8916,7 +8925,7 @@
         <v>36</v>
       </c>
       <c r="S87" s="4" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="88" spans="1:19">
@@ -8924,19 +8933,19 @@
         <v>5</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="K88" s="3">
         <v>0</v>
@@ -8948,7 +8957,7 @@
         <v>36</v>
       </c>
       <c r="S88" s="3" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="89" spans="1:19">
@@ -8956,19 +8965,19 @@
         <v>5</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I89" s="4" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="K89" s="3">
         <v>0</v>
@@ -8980,7 +8989,7 @@
         <v>36</v>
       </c>
       <c r="S89" s="4" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="90" spans="1:19">
@@ -8988,19 +8997,19 @@
         <v>5</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="K90" s="3">
         <v>0</v>
@@ -9012,7 +9021,7 @@
         <v>36</v>
       </c>
       <c r="S90" s="3" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="91" spans="1:19">
@@ -9020,19 +9029,19 @@
         <v>5</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I91" s="4" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -9044,7 +9053,7 @@
         <v>36</v>
       </c>
       <c r="S91" s="4" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="92" spans="1:19">
@@ -9052,19 +9061,19 @@
         <v>5</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="K92" s="3">
         <v>0</v>
@@ -9076,7 +9085,7 @@
         <v>36</v>
       </c>
       <c r="S92" s="3" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="93" spans="1:19">
@@ -9084,19 +9093,19 @@
         <v>5</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I93" s="4" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="K93" s="3">
         <v>0</v>
@@ -9108,7 +9117,7 @@
         <v>36</v>
       </c>
       <c r="S93" s="4" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="94" spans="1:19">
@@ -9116,19 +9125,19 @@
         <v>5</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="G94" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="K94" s="3">
         <v>0</v>
@@ -9140,7 +9149,7 @@
         <v>36</v>
       </c>
       <c r="S94" s="3" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="95" spans="1:19">
@@ -9148,19 +9157,19 @@
         <v>5</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="I95" s="4" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="K95" s="3">
         <v>0</v>
@@ -9172,7 +9181,7 @@
         <v>36</v>
       </c>
       <c r="S95" s="4" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="96" spans="1:19">
@@ -9180,19 +9189,19 @@
         <v>5</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="G96" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -9204,7 +9213,7 @@
         <v>36</v>
       </c>
       <c r="S96" s="3" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="97" spans="1:19">
@@ -9212,16 +9221,16 @@
         <v>5</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I97" s="4" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="K97" s="3">
         <v>0</v>
@@ -9230,10 +9239,10 @@
         <v>0</v>
       </c>
       <c r="P97" s="4" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="S97" s="4" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="98" spans="1:19">
@@ -9241,19 +9250,19 @@
         <v>5</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="G98" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="K98" s="3">
         <v>0</v>
@@ -9265,7 +9274,7 @@
         <v>36</v>
       </c>
       <c r="S98" s="3" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="99" spans="1:19">
@@ -9273,19 +9282,19 @@
         <v>5</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I99" s="4" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="K99" s="3">
         <v>0</v>
@@ -9297,7 +9306,7 @@
         <v>36</v>
       </c>
       <c r="S99" s="4" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="100" spans="1:19">
@@ -9305,19 +9314,19 @@
         <v>5</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="G100" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="K100" s="3">
         <v>0</v>
@@ -9329,7 +9338,7 @@
         <v>36</v>
       </c>
       <c r="S100" s="3" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="101" spans="1:19">
@@ -9337,19 +9346,19 @@
         <v>5</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="G101" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I101" s="4" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -9361,7 +9370,7 @@
         <v>36</v>
       </c>
       <c r="S101" s="4" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="102" spans="1:19">
@@ -9369,19 +9378,19 @@
         <v>5</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="G102" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="K102" s="3">
         <v>0</v>
@@ -9393,7 +9402,7 @@
         <v>36</v>
       </c>
       <c r="S102" s="3" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="103" spans="1:19">
@@ -9401,19 +9410,19 @@
         <v>5</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="I103" s="4" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="K103" s="3">
         <v>0</v>
@@ -9425,7 +9434,7 @@
         <v>36</v>
       </c>
       <c r="S103" s="4" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="104" spans="1:19">
@@ -9433,19 +9442,19 @@
         <v>5</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="G104" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I104" s="3" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="K104" s="3">
         <v>0</v>
@@ -9457,7 +9466,7 @@
         <v>36</v>
       </c>
       <c r="S104" s="3" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="105" spans="1:19">
@@ -9465,19 +9474,19 @@
         <v>5</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="I105" s="4" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="K105" s="3">
         <v>0</v>
@@ -9489,7 +9498,7 @@
         <v>36</v>
       </c>
       <c r="S105" s="4" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="106" spans="1:19">
@@ -9497,19 +9506,19 @@
         <v>5</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="G106" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I106" s="3" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K106" s="3">
         <v>0</v>
@@ -9521,7 +9530,7 @@
         <v>36</v>
       </c>
       <c r="S106" s="3" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="107" spans="1:19">
@@ -9529,19 +9538,19 @@
         <v>5</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="G107" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I107" s="4" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="K107" s="3">
         <v>0</v>
@@ -9553,7 +9562,7 @@
         <v>36</v>
       </c>
       <c r="S107" s="4" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="108" spans="1:19">
@@ -9561,19 +9570,19 @@
         <v>5</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="G108" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I108" s="3" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="K108" s="3">
         <v>0</v>
@@ -9585,7 +9594,7 @@
         <v>36</v>
       </c>
       <c r="S108" s="3" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="109" spans="1:19">
@@ -9593,19 +9602,19 @@
         <v>5</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="G109" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I109" s="4" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="K109" s="3">
         <v>0</v>
@@ -9617,7 +9626,7 @@
         <v>36</v>
       </c>
       <c r="S109" s="4" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="110" spans="1:19">
@@ -9625,19 +9634,19 @@
         <v>5</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="G110" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I110" s="3" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="K110" s="3">
         <v>0</v>
@@ -9649,7 +9658,7 @@
         <v>36</v>
       </c>
       <c r="S110" s="3" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="111" spans="1:19">
@@ -9657,19 +9666,19 @@
         <v>5</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="G111" s="4" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I111" s="4" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="K111" s="3">
         <v>0</v>
@@ -9681,7 +9690,7 @@
         <v>36</v>
       </c>
       <c r="S111" s="4" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="112" spans="1:19">
@@ -9689,19 +9698,19 @@
         <v>5</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="G112" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I112" s="3" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="K112" s="3">
         <v>0</v>
@@ -9713,7 +9722,7 @@
         <v>36</v>
       </c>
       <c r="S112" s="3" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="113" spans="1:19">
@@ -9721,16 +9730,16 @@
         <v>6</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="H113" s="3">
         <v>600</v>
       </c>
       <c r="I113" s="4" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="K113" s="3">
         <v>0</v>
@@ -9739,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="P113" s="4" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="S113" s="4" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="114" spans="1:19">
@@ -9750,16 +9759,16 @@
         <v>6</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="H114" s="3">
         <v>450</v>
       </c>
       <c r="I114" s="3" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="K114" s="3">
         <v>0</v>
@@ -9771,7 +9780,7 @@
         <v>36</v>
       </c>
       <c r="S114" s="3" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="115" spans="1:19">
@@ -9779,16 +9788,16 @@
         <v>6</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="H115" s="3">
         <v>550</v>
       </c>
       <c r="I115" s="4" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K115" s="3">
         <v>0</v>
@@ -9800,7 +9809,7 @@
         <v>36</v>
       </c>
       <c r="S115" s="4" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="116" spans="1:19">
@@ -9808,16 +9817,16 @@
         <v>6</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="H116" s="3">
         <v>1000</v>
       </c>
       <c r="I116" s="3" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="K116" s="3">
         <v>0</v>
@@ -9829,7 +9838,7 @@
         <v>36</v>
       </c>
       <c r="S116" s="3" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="117" spans="1:19">
@@ -9837,16 +9846,16 @@
         <v>6</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="H117" s="3">
         <v>750</v>
       </c>
       <c r="I117" s="4" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="K117" s="3">
         <v>0</v>
@@ -9858,7 +9867,7 @@
         <v>36</v>
       </c>
       <c r="S117" s="4" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="118" spans="1:19">
@@ -9866,16 +9875,16 @@
         <v>6</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="H118" s="3">
         <v>850</v>
       </c>
       <c r="I118" s="3" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="K118" s="3">
         <v>0</v>
@@ -9887,7 +9896,7 @@
         <v>36</v>
       </c>
       <c r="S118" s="3" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="119" spans="1:19">
@@ -9895,16 +9904,16 @@
         <v>6</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="H119" s="3">
         <v>1000</v>
       </c>
       <c r="I119" s="4" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="K119" s="3">
         <v>0</v>
@@ -9916,7 +9925,7 @@
         <v>36</v>
       </c>
       <c r="S119" s="4" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="120" spans="1:19">
@@ -9924,16 +9933,16 @@
         <v>6</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="H120" s="3">
         <v>750</v>
       </c>
       <c r="I120" s="3" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="K120" s="3">
         <v>0</v>
@@ -9945,7 +9954,7 @@
         <v>36</v>
       </c>
       <c r="S120" s="3" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="121" spans="1:19">
@@ -9953,16 +9962,16 @@
         <v>6</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="H121" s="3">
         <v>850</v>
       </c>
       <c r="I121" s="4" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="K121" s="3">
         <v>0</v>
@@ -9974,7 +9983,7 @@
         <v>36</v>
       </c>
       <c r="S121" s="4" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="122" spans="1:19">
@@ -9982,16 +9991,16 @@
         <v>6</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="H122" s="3">
         <v>500</v>
       </c>
       <c r="I122" s="3" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="K122" s="3">
         <v>0</v>
@@ -10003,7 +10012,7 @@
         <v>36</v>
       </c>
       <c r="S122" s="3" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="123" spans="1:19">
@@ -10011,16 +10020,16 @@
         <v>6</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C123" s="4" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="H123" s="3">
         <v>1000</v>
       </c>
       <c r="I123" s="4" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="K123" s="3">
         <v>0</v>
@@ -10032,7 +10041,7 @@
         <v>36</v>
       </c>
       <c r="S123" s="4" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="124" spans="1:19">
@@ -10040,16 +10049,16 @@
         <v>6</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="H124" s="3">
         <v>600</v>
       </c>
       <c r="I124" s="3" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="K124" s="3">
         <v>0</v>
@@ -10061,7 +10070,7 @@
         <v>36</v>
       </c>
       <c r="S124" s="3" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="125" spans="1:19">
@@ -10069,16 +10078,16 @@
         <v>6</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="H125" s="3">
         <v>750</v>
       </c>
       <c r="I125" s="4" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="K125" s="3">
         <v>0</v>
@@ -10090,7 +10099,7 @@
         <v>36</v>
       </c>
       <c r="S125" s="4" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="126" spans="1:19">
@@ -10098,16 +10107,16 @@
         <v>6</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="H126" s="3">
         <v>850</v>
       </c>
       <c r="I126" s="3" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="K126" s="3">
         <v>0</v>
@@ -10119,7 +10128,7 @@
         <v>36</v>
       </c>
       <c r="S126" s="3" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="127" spans="1:19">
@@ -10127,16 +10136,16 @@
         <v>6</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C127" s="4" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="H127" s="3">
         <v>400</v>
       </c>
       <c r="I127" s="4" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="K127" s="3">
         <v>0</v>
@@ -10148,7 +10157,7 @@
         <v>36</v>
       </c>
       <c r="S127" s="4" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="128" spans="1:19">
@@ -10156,13 +10165,13 @@
         <v>7</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="I128" s="3" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="K128" s="3">
         <v>0</v>
@@ -10171,10 +10180,10 @@
         <v>0</v>
       </c>
       <c r="P128" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="S128" s="3" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="129" spans="1:19">
@@ -10182,16 +10191,16 @@
         <v>7</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C129" s="4" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="I129" s="4" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="K129" s="3">
         <v>0</v>
@@ -10203,7 +10212,7 @@
         <v>36</v>
       </c>
       <c r="S129" s="4" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="130" spans="1:19">
@@ -10211,16 +10220,16 @@
         <v>7</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="I130" s="3" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="K130" s="3">
         <v>0</v>
@@ -10232,7 +10241,7 @@
         <v>36</v>
       </c>
       <c r="S130" s="3" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="131" spans="1:19">
@@ -10240,16 +10249,16 @@
         <v>7</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C131" s="4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="I131" s="4" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="K131" s="3">
         <v>0</v>
@@ -10261,7 +10270,7 @@
         <v>36</v>
       </c>
       <c r="S131" s="4" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="132" spans="1:19">
@@ -10269,16 +10278,16 @@
         <v>7</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="I132" s="3" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="K132" s="3">
         <v>0</v>
@@ -10290,7 +10299,7 @@
         <v>36</v>
       </c>
       <c r="S132" s="3" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="133" spans="1:19">
@@ -10298,16 +10307,16 @@
         <v>7</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C133" s="4" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="I133" s="4" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="K133" s="3">
         <v>0</v>
@@ -10319,7 +10328,7 @@
         <v>36</v>
       </c>
       <c r="S133" s="4" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="134" spans="1:19">
@@ -10327,16 +10336,16 @@
         <v>7</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="I134" s="3" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="K134" s="3">
         <v>0</v>
@@ -10348,7 +10357,7 @@
         <v>36</v>
       </c>
       <c r="S134" s="3" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="135" spans="1:19">
@@ -10356,16 +10365,16 @@
         <v>7</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C135" s="4" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="I135" s="4" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="K135" s="3">
         <v>0</v>
@@ -10377,7 +10386,7 @@
         <v>36</v>
       </c>
       <c r="S135" s="4" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="136" spans="1:19">
@@ -10385,16 +10394,16 @@
         <v>7</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="I136" s="3" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="K136" s="3">
         <v>0</v>
@@ -10406,7 +10415,7 @@
         <v>36</v>
       </c>
       <c r="S136" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="137" spans="1:19">
@@ -10414,16 +10423,16 @@
         <v>7</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C137" s="4" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="I137" s="4" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="K137" s="3">
         <v>0</v>
@@ -10435,7 +10444,7 @@
         <v>36</v>
       </c>
       <c r="S137" s="4" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="138" spans="1:19">
@@ -10443,16 +10452,16 @@
         <v>7</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="I138" s="3" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="K138" s="3">
         <v>0</v>
@@ -10464,7 +10473,7 @@
         <v>36</v>
       </c>
       <c r="S138" s="3" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="139" spans="1:19">
@@ -10472,16 +10481,16 @@
         <v>7</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C139" s="4" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="I139" s="4" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="K139" s="3">
         <v>0</v>
@@ -10493,7 +10502,7 @@
         <v>36</v>
       </c>
       <c r="S139" s="4" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="140" spans="1:19">
@@ -10501,16 +10510,16 @@
         <v>7</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="I140" s="3" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="K140" s="3">
         <v>0</v>
@@ -10522,7 +10531,7 @@
         <v>36</v>
       </c>
       <c r="S140" s="3" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="141" spans="1:19">
@@ -10530,16 +10539,16 @@
         <v>7</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="I141" s="4" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="K141" s="3">
         <v>0</v>
@@ -10551,7 +10560,7 @@
         <v>36</v>
       </c>
       <c r="S141" s="4" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="142" spans="1:19">
@@ -10559,16 +10568,16 @@
         <v>7</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="I142" s="3" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="K142" s="3">
         <v>0</v>
@@ -10580,7 +10589,7 @@
         <v>36</v>
       </c>
       <c r="S142" s="3" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="143" spans="1:19">
@@ -10588,16 +10597,16 @@
         <v>7</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C143" s="4" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="I143" s="4" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="K143" s="3">
         <v>0</v>
@@ -10609,7 +10618,7 @@
         <v>36</v>
       </c>
       <c r="S143" s="4" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="144" spans="1:19">
@@ -10617,16 +10626,16 @@
         <v>7</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="I144" s="3" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="K144" s="3">
         <v>0</v>
@@ -10638,7 +10647,7 @@
         <v>36</v>
       </c>
       <c r="S144" s="3" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="145" spans="1:19">
@@ -10646,16 +10655,16 @@
         <v>7</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C145" s="4" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="I145" s="4" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="K145" s="3">
         <v>0</v>
@@ -10667,7 +10676,7 @@
         <v>36</v>
       </c>
       <c r="S145" s="4" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="146" spans="1:19">
@@ -10675,16 +10684,16 @@
         <v>7</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="I146" s="3" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="K146" s="3">
         <v>0</v>
@@ -10696,7 +10705,7 @@
         <v>36</v>
       </c>
       <c r="S146" s="3" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="147" spans="1:19">
@@ -10704,13 +10713,13 @@
         <v>8</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>460</v>
+        <v>146</v>
       </c>
       <c r="I147" s="4" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="K147" s="3">
         <v>0</v>
@@ -10722,7 +10731,7 @@
         <v>36</v>
       </c>
       <c r="S147" s="4" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="148" spans="1:19">
@@ -10730,13 +10739,13 @@
         <v>8</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>460</v>
+        <v>146</v>
       </c>
       <c r="I148" s="3" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="K148" s="3">
         <v>0</v>
@@ -10748,7 +10757,7 @@
         <v>36</v>
       </c>
       <c r="S148" s="3" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="149" spans="1:19">
@@ -10756,13 +10765,13 @@
         <v>8</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>460</v>
+        <v>146</v>
       </c>
       <c r="I149" s="4" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="K149" s="3">
         <v>0</v>
@@ -10774,7 +10783,7 @@
         <v>36</v>
       </c>
       <c r="S149" s="4" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="150" spans="1:19">
@@ -10782,13 +10791,13 @@
         <v>8</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>460</v>
+        <v>146</v>
       </c>
       <c r="I150" s="3" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="K150" s="3">
         <v>0</v>
@@ -10800,7 +10809,7 @@
         <v>36</v>
       </c>
       <c r="S150" s="3" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="151" spans="1:19">
@@ -10808,13 +10817,13 @@
         <v>8</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D151" s="4" t="s">
-        <v>460</v>
+        <v>146</v>
       </c>
       <c r="I151" s="4" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="K151" s="3">
         <v>0</v>
@@ -10826,7 +10835,7 @@
         <v>36</v>
       </c>
       <c r="S151" s="4" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="152" spans="1:19">
@@ -10834,13 +10843,13 @@
         <v>8</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D152" s="3" t="s">
-        <v>460</v>
+        <v>146</v>
       </c>
       <c r="I152" s="3" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="K152" s="3">
         <v>0</v>
@@ -10852,7 +10861,7 @@
         <v>36</v>
       </c>
       <c r="S152" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="153" spans="1:19">
@@ -10860,13 +10869,13 @@
         <v>8</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>460</v>
+        <v>146</v>
       </c>
       <c r="I153" s="4" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="K153" s="3">
         <v>0</v>
@@ -10878,7 +10887,7 @@
         <v>36</v>
       </c>
       <c r="S153" s="4" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="154" spans="1:19">
@@ -10886,13 +10895,13 @@
         <v>8</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D154" s="3" t="s">
-        <v>460</v>
+        <v>146</v>
       </c>
       <c r="I154" s="3" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="K154" s="3">
         <v>0</v>
@@ -10904,7 +10913,7 @@
         <v>36</v>
       </c>
       <c r="S154" s="3" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="155" spans="1:19">
@@ -10912,13 +10921,13 @@
         <v>8</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>460</v>
+        <v>146</v>
       </c>
       <c r="I155" s="4" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="K155" s="3">
         <v>0</v>
@@ -10930,7 +10939,7 @@
         <v>36</v>
       </c>
       <c r="S155" s="4" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="156" spans="1:19">
@@ -10938,16 +10947,16 @@
         <v>9</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H156" s="3">
         <v>1000</v>
       </c>
       <c r="I156" s="3" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="K156" s="3">
         <v>0</v>
@@ -10959,7 +10968,7 @@
         <v>36</v>
       </c>
       <c r="S156" s="3" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="157" spans="1:19">
@@ -10967,16 +10976,16 @@
         <v>9</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H157" s="3">
         <v>250</v>
       </c>
       <c r="I157" s="4" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="K157" s="3">
         <v>0</v>
@@ -10988,7 +10997,7 @@
         <v>36</v>
       </c>
       <c r="S157" s="4" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="158" spans="1:19">
@@ -10996,16 +11005,16 @@
         <v>9</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H158" s="3">
         <v>500</v>
       </c>
       <c r="I158" s="3" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="K158" s="3">
         <v>0</v>
@@ -11017,7 +11026,7 @@
         <v>36</v>
       </c>
       <c r="S158" s="3" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="159" spans="1:19">
@@ -11025,16 +11034,16 @@
         <v>9</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H159" s="3">
         <v>240</v>
       </c>
       <c r="I159" s="4" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="K159" s="3">
         <v>0</v>
@@ -11046,7 +11055,7 @@
         <v>36</v>
       </c>
       <c r="S159" s="4" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="160" spans="1:19">
@@ -11054,16 +11063,16 @@
         <v>9</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H160" s="3">
         <v>480</v>
       </c>
       <c r="I160" s="3" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="K160" s="3">
         <v>0</v>
@@ -11075,7 +11084,7 @@
         <v>36</v>
       </c>
       <c r="S160" s="3" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="161" spans="1:19">
@@ -11083,16 +11092,16 @@
         <v>9</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H161" s="3">
         <v>960</v>
       </c>
       <c r="I161" s="4" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="K161" s="3">
         <v>0</v>
@@ -11104,7 +11113,7 @@
         <v>36</v>
       </c>
       <c r="S161" s="4" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="162" spans="1:19">
@@ -11112,16 +11121,16 @@
         <v>9</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H162" s="3">
         <v>1000</v>
       </c>
       <c r="I162" s="3" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="K162" s="3">
         <v>0</v>
@@ -11133,7 +11142,7 @@
         <v>36</v>
       </c>
       <c r="S162" s="3" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="163" spans="1:19">
@@ -11141,16 +11150,16 @@
         <v>9</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D163" s="4" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H163" s="3">
         <v>250</v>
       </c>
       <c r="I163" s="4" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="K163" s="3">
         <v>0</v>
@@ -11162,7 +11171,7 @@
         <v>36</v>
       </c>
       <c r="S163" s="4" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="164" spans="1:19">
@@ -11170,16 +11179,16 @@
         <v>9</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H164" s="3">
         <v>500</v>
       </c>
       <c r="I164" s="3" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="K164" s="3">
         <v>0</v>
@@ -11191,7 +11200,7 @@
         <v>36</v>
       </c>
       <c r="S164" s="3" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="165" spans="1:19">
@@ -11199,16 +11208,16 @@
         <v>9</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D165" s="4" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H165" s="3">
         <v>2000</v>
       </c>
       <c r="I165" s="4" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="K165" s="3">
         <v>0</v>
@@ -11220,7 +11229,7 @@
         <v>36</v>
       </c>
       <c r="S165" s="4" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="166" spans="1:19">
@@ -11228,16 +11237,16 @@
         <v>9</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H166" s="3">
         <v>4000</v>
       </c>
       <c r="I166" s="3" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="K166" s="3">
         <v>0</v>
@@ -11249,7 +11258,7 @@
         <v>36</v>
       </c>
       <c r="S166" s="3" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="167" spans="1:19">
@@ -11257,16 +11266,16 @@
         <v>10</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D167" s="4" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H167" s="3">
         <v>2000</v>
       </c>
       <c r="I167" s="4" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="K167" s="3">
         <v>0</v>
@@ -11278,7 +11287,7 @@
         <v>36</v>
       </c>
       <c r="S167" s="4" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="168" spans="1:19">
@@ -11286,16 +11295,16 @@
         <v>10</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H168" s="3">
         <v>1000</v>
       </c>
       <c r="I168" s="3" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="K168" s="3">
         <v>0</v>
@@ -11307,7 +11316,7 @@
         <v>36</v>
       </c>
       <c r="S168" s="3" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="169" spans="1:19">
@@ -11315,16 +11324,16 @@
         <v>10</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D169" s="4" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H169" s="3">
         <v>1000</v>
       </c>
       <c r="I169" s="4" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="K169" s="3">
         <v>0</v>
@@ -11336,7 +11345,7 @@
         <v>36</v>
       </c>
       <c r="S169" s="4" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="170" spans="1:19">
@@ -11344,16 +11353,16 @@
         <v>10</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D170" s="3" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H170" s="3">
         <v>500</v>
       </c>
       <c r="I170" s="3" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="K170" s="3">
         <v>0</v>
@@ -11365,7 +11374,7 @@
         <v>36</v>
       </c>
       <c r="S170" s="3" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="171" spans="1:19">
@@ -11373,16 +11382,16 @@
         <v>10</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H171" s="3">
         <v>1000</v>
       </c>
       <c r="I171" s="4" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="K171" s="3">
         <v>0</v>
@@ -11394,7 +11403,7 @@
         <v>36</v>
       </c>
       <c r="S171" s="4" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="172" spans="1:19">
@@ -11402,16 +11411,16 @@
         <v>10</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="D172" s="3" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H172" s="3">
         <v>2000</v>
       </c>
       <c r="I172" s="3" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="K172" s="3">
         <v>0</v>
@@ -11423,7 +11432,7 @@
         <v>36</v>
       </c>
       <c r="S172" s="3" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="173" spans="1:19">
@@ -11431,16 +11440,16 @@
         <v>10</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H173" s="3">
         <v>1000</v>
       </c>
       <c r="I173" s="4" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="K173" s="3">
         <v>0</v>
@@ -11452,7 +11461,7 @@
         <v>36</v>
       </c>
       <c r="S173" s="4" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="174" spans="1:19">
@@ -11460,16 +11469,16 @@
         <v>10</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H174" s="3">
         <v>500</v>
       </c>
       <c r="I174" s="3" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="K174" s="3">
         <v>0</v>
@@ -11481,7 +11490,7 @@
         <v>36</v>
       </c>
       <c r="S174" s="3" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="175" spans="1:19">
@@ -11489,16 +11498,16 @@
         <v>10</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H175" s="3">
         <v>1000</v>
       </c>
       <c r="I175" s="4" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="K175" s="3">
         <v>0</v>
@@ -11510,7 +11519,7 @@
         <v>36</v>
       </c>
       <c r="S175" s="4" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="176" spans="1:19">
@@ -11518,16 +11527,16 @@
         <v>10</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H176" s="3">
         <v>1000</v>
       </c>
       <c r="I176" s="3" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="K176" s="3">
         <v>0</v>
@@ -11539,7 +11548,7 @@
         <v>36</v>
       </c>
       <c r="S176" s="3" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="177" spans="1:19">
@@ -11547,16 +11556,16 @@
         <v>10</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D177" s="4" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H177" s="3">
         <v>1000</v>
       </c>
       <c r="I177" s="4" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="K177" s="3">
         <v>0</v>
@@ -11568,7 +11577,7 @@
         <v>36</v>
       </c>
       <c r="S177" s="4" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="178" spans="1:19">
@@ -11576,16 +11585,16 @@
         <v>10</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D178" s="3" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H178" s="3">
         <v>1000</v>
       </c>
       <c r="I178" s="3" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="K178" s="3">
         <v>0</v>
@@ -11597,7 +11606,7 @@
         <v>36</v>
       </c>
       <c r="S178" s="3" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="179" spans="1:19">
@@ -11605,16 +11614,16 @@
         <v>10</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H179" s="3">
         <v>2000</v>
       </c>
       <c r="I179" s="4" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="K179" s="3">
         <v>0</v>
@@ -11626,7 +11635,7 @@
         <v>36</v>
       </c>
       <c r="S179" s="4" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="180" spans="1:19">
@@ -11634,13 +11643,13 @@
         <v>11</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H180" s="3">
         <v>900</v>
       </c>
       <c r="I180" s="3" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="K180" s="3">
         <v>0</v>
@@ -11652,7 +11661,7 @@
         <v>36</v>
       </c>
       <c r="S180" s="3" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="181" spans="1:19">
@@ -11660,13 +11669,13 @@
         <v>11</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H181" s="3">
         <v>2000</v>
       </c>
       <c r="I181" s="4" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="K181" s="3">
         <v>0</v>
@@ -11678,7 +11687,7 @@
         <v>36</v>
       </c>
       <c r="S181" s="4" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="182" spans="1:19">
@@ -11686,13 +11695,13 @@
         <v>11</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H182" s="3">
         <v>1200</v>
       </c>
       <c r="I182" s="3" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="K182" s="3">
         <v>0</v>
@@ -11704,7 +11713,7 @@
         <v>36</v>
       </c>
       <c r="S182" s="3" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="183" spans="1:19">
@@ -11712,13 +11721,13 @@
         <v>11</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H183" s="3">
         <v>8000</v>
       </c>
       <c r="I183" s="4" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="K183" s="3">
         <v>0</v>
@@ -11730,7 +11739,7 @@
         <v>36</v>
       </c>
       <c r="S183" s="4" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="184" spans="1:19">
@@ -11738,13 +11747,13 @@
         <v>11</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H184" s="3">
         <v>4000</v>
       </c>
       <c r="I184" s="3" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="K184" s="3">
         <v>0</v>
@@ -11756,7 +11765,7 @@
         <v>36</v>
       </c>
       <c r="S184" s="3" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="185" spans="1:19">
@@ -11764,13 +11773,13 @@
         <v>11</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H185" s="3">
         <v>1000</v>
       </c>
       <c r="I185" s="4" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="K185" s="3">
         <v>0</v>
@@ -11782,7 +11791,7 @@
         <v>36</v>
       </c>
       <c r="S185" s="4" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="186" spans="1:19">
@@ -11790,13 +11799,13 @@
         <v>11</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H186" s="3">
         <v>10000</v>
       </c>
       <c r="I186" s="3" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="K186" s="3">
         <v>0</v>
@@ -11808,7 +11817,7 @@
         <v>36</v>
       </c>
       <c r="S186" s="3" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="187" spans="1:19">
@@ -11816,13 +11825,13 @@
         <v>11</v>
       </c>
       <c r="B187" s="4" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H187" s="3">
         <v>6000</v>
       </c>
       <c r="I187" s="4" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="K187" s="3">
         <v>0</v>
@@ -11834,7 +11843,7 @@
         <v>36</v>
       </c>
       <c r="S187" s="4" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
   </sheetData>
@@ -11842,11 +11851,12 @@
   <hyperlinks>
     <hyperlink ref="R25" r:id="rId1"/>
     <hyperlink ref="Q48" r:id="rId2"/>
-    <hyperlink ref="Q49" r:id="rId3"/>
-    <hyperlink ref="Q50" r:id="rId4"/>
-    <hyperlink ref="Q51" r:id="rId5"/>
-    <hyperlink ref="Q52" r:id="rId6"/>
-    <hyperlink ref="Q53" r:id="rId7"/>
+    <hyperlink ref="R48" r:id="rId3"/>
+    <hyperlink ref="Q49" r:id="rId4"/>
+    <hyperlink ref="Q50" r:id="rId5"/>
+    <hyperlink ref="Q51" r:id="rId6"/>
+    <hyperlink ref="Q52" r:id="rId7"/>
+    <hyperlink ref="Q53" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -13069,6 +13079,9 @@
       <c r="A2" s="3" t="s">
         <v>145</v>
       </c>
+      <c r="C2" s="3" t="s">
+        <v>146</v>
+      </c>
       <c r="D2" s="3">
         <v>6</v>
       </c>
@@ -13076,10 +13089,10 @@
         <v>12</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J2" s="3">
         <v>0</v>
@@ -13091,15 +13104,18 @@
         <v>36</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>93</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D3" s="3">
         <v>6</v>
@@ -13108,10 +13124,10 @@
         <v>12</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="J3" s="3">
         <v>0</v>
@@ -13123,15 +13139,15 @@
         <v>36</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="R3" s="4" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="4" spans="1:18">
       <c r="A4" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D4" s="3">
         <v>6</v>
@@ -13140,10 +13156,10 @@
         <v>12</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="J4" s="3">
         <v>0</v>
@@ -13155,15 +13171,15 @@
         <v>36</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="5" spans="1:18">
       <c r="A5" s="4" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D5" s="3">
         <v>6</v>
@@ -13172,10 +13188,10 @@
         <v>12</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="J5" s="3">
         <v>0</v>
@@ -13187,15 +13203,15 @@
         <v>36</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="6" spans="1:18">
       <c r="A6" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D6" s="3">
         <v>6</v>
@@ -13204,10 +13220,10 @@
         <v>12</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="J6" s="3">
         <v>0</v>
@@ -13219,15 +13235,15 @@
         <v>36</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="7" spans="1:18">
       <c r="A7" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D7" s="3">
         <v>6</v>
@@ -13236,10 +13252,10 @@
         <v>12</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="J7" s="3">
         <v>0</v>
@@ -13251,15 +13267,15 @@
         <v>36</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="R7" s="4" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="8" spans="1:18">
       <c r="A8" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D8" s="3">
         <v>6</v>
@@ -13268,10 +13284,10 @@
         <v>12</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="J8" s="3">
         <v>0</v>
@@ -13283,12 +13299,12 @@
         <v>36</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D9" s="3">
         <v>8</v>
@@ -13297,10 +13313,10 @@
         <v>16</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="J9" s="3">
         <v>0</v>
@@ -13309,15 +13325,15 @@
         <v>0</v>
       </c>
       <c r="O9" s="4" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="R9" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D10" s="3">
         <v>8</v>
@@ -13326,10 +13342,10 @@
         <v>16</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="J10" s="3">
         <v>0</v>
@@ -13341,12 +13357,12 @@
         <v>36</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11" spans="1:18">
       <c r="A11" s="4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D11" s="3">
         <v>8</v>
@@ -13355,10 +13371,10 @@
         <v>16</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="J11" s="3">
         <v>0</v>
@@ -13370,12 +13386,12 @@
         <v>36</v>
       </c>
       <c r="R11" s="4" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12" spans="1:18">
       <c r="A12" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D12" s="3">
         <v>8</v>
@@ -13384,10 +13400,10 @@
         <v>16</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="J12" s="3">
         <v>0</v>
@@ -13399,12 +13415,12 @@
         <v>36</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="4" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D13" s="3">
         <v>8</v>
@@ -13413,10 +13429,10 @@
         <v>16</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="J13" s="3">
         <v>0</v>
@@ -13428,12 +13444,12 @@
         <v>36</v>
       </c>
       <c r="R13" s="4" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D14" s="3">
         <v>8</v>
@@ -13442,10 +13458,10 @@
         <v>16</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="J14" s="3">
         <v>0</v>
@@ -13457,12 +13473,12 @@
         <v>36</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="15" spans="1:18">
       <c r="A15" s="4" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D15" s="3">
         <v>8</v>
@@ -13471,10 +13487,10 @@
         <v>16</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="J15" s="3">
         <v>0</v>
@@ -13486,12 +13502,12 @@
         <v>36</v>
       </c>
       <c r="R15" s="4" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="16" spans="1:18">
       <c r="A16" s="3" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D16" s="3">
         <v>8</v>
@@ -13500,10 +13516,10 @@
         <v>16</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="J16" s="3">
         <v>0</v>
@@ -13515,12 +13531,12 @@
         <v>36</v>
       </c>
       <c r="R16" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="17" spans="1:18">
       <c r="A17" s="4" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D17" s="3">
         <v>8</v>
@@ -13529,10 +13545,10 @@
         <v>16</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="J17" s="3">
         <v>0</v>
@@ -13544,12 +13560,12 @@
         <v>36</v>
       </c>
       <c r="R17" s="4" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="18" spans="1:18">
       <c r="A18" s="3" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D18" s="3">
         <v>12</v>
@@ -13558,10 +13574,10 @@
         <v>24</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="J18" s="3">
         <v>0</v>
@@ -13573,12 +13589,12 @@
         <v>36</v>
       </c>
       <c r="R18" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="19" spans="1:18">
       <c r="A19" s="4" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D19" s="3">
         <v>16</v>
@@ -13587,10 +13603,10 @@
         <v>32</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="J19" s="3">
         <v>0</v>
@@ -13602,12 +13618,12 @@
         <v>36</v>
       </c>
       <c r="R19" s="4" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="20" spans="1:18">
       <c r="A20" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D20" s="3">
         <v>16</v>
@@ -13616,10 +13632,10 @@
         <v>32</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="J20" s="3">
         <v>0</v>
@@ -13631,12 +13647,12 @@
         <v>36</v>
       </c>
       <c r="R20" s="3" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="21" spans="1:18">
       <c r="A21" s="4" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D21" s="3">
         <v>6</v>
@@ -13645,10 +13661,10 @@
         <v>12</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="J21" s="3">
         <v>0</v>
@@ -13660,12 +13676,12 @@
         <v>36</v>
       </c>
       <c r="R21" s="4" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="22" spans="1:18">
       <c r="A22" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D22" s="3">
         <v>6</v>
@@ -13674,10 +13690,10 @@
         <v>12</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="J22" s="3">
         <v>0</v>
@@ -13689,12 +13705,12 @@
         <v>36</v>
       </c>
       <c r="R22" s="3" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="23" spans="1:18">
       <c r="A23" s="4" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D23" s="3">
         <v>6</v>
@@ -13703,10 +13719,10 @@
         <v>12</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="J23" s="3">
         <v>0</v>
@@ -13718,12 +13734,12 @@
         <v>36</v>
       </c>
       <c r="R23" s="4" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="24" spans="1:18">
       <c r="A24" s="3" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D24" s="3">
         <v>10</v>
@@ -13732,10 +13748,10 @@
         <v>16</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="J24" s="3">
         <v>0</v>
@@ -13747,12 +13763,12 @@
         <v>36</v>
       </c>
       <c r="R24" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="25" spans="1:18">
       <c r="A25" s="4" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D25" s="3">
         <v>14</v>
@@ -13761,10 +13777,10 @@
         <v>20</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J25" s="3">
         <v>0</v>
@@ -13776,12 +13792,12 @@
         <v>36</v>
       </c>
       <c r="R25" s="4" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="26" spans="1:18">
       <c r="A26" s="3" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D26" s="3">
         <v>14</v>
@@ -13790,10 +13806,10 @@
         <v>20</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J26" s="3">
         <v>0</v>
@@ -13805,12 +13821,12 @@
         <v>36</v>
       </c>
       <c r="R26" s="3" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="27" spans="1:18">
       <c r="A27" s="4" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="D27" s="3">
         <v>8</v>
@@ -13819,10 +13835,10 @@
         <v>16</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="J27" s="3">
         <v>0</v>
@@ -13834,12 +13850,12 @@
         <v>36</v>
       </c>
       <c r="R27" s="4" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="28" spans="1:18">
       <c r="A28" s="3" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D28" s="3">
         <v>12</v>
@@ -13848,10 +13864,10 @@
         <v>20</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="J28" s="3">
         <v>0</v>
@@ -13863,12 +13879,12 @@
         <v>36</v>
       </c>
       <c r="R28" s="3" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="29" spans="1:18">
       <c r="A29" s="4" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D29" s="3">
         <v>16</v>
@@ -13877,10 +13893,10 @@
         <v>24</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="J29" s="3">
         <v>0</v>
@@ -13892,12 +13908,12 @@
         <v>36</v>
       </c>
       <c r="R29" s="4" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="30" spans="1:18">
       <c r="A30" s="3" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D30" s="3">
         <v>20</v>
@@ -13906,10 +13922,10 @@
         <v>28</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="J30" s="3">
         <v>0</v>
@@ -13921,12 +13937,12 @@
         <v>36</v>
       </c>
       <c r="R30" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="31" spans="1:18">
       <c r="A31" s="4" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D31" s="3">
         <v>4</v>
@@ -13935,10 +13951,10 @@
         <v>8</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="J31" s="3">
         <v>0</v>
@@ -13950,12 +13966,12 @@
         <v>36</v>
       </c>
       <c r="R31" s="4" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="32" spans="1:18">
       <c r="A32" s="3" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D32" s="3">
         <v>4</v>
@@ -13964,10 +13980,10 @@
         <v>8</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="J32" s="3">
         <v>0</v>
@@ -13979,12 +13995,12 @@
         <v>36</v>
       </c>
       <c r="R32" s="3" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="33" spans="1:18">
       <c r="A33" s="4" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D33" s="3">
         <v>4</v>
@@ -13993,10 +14009,10 @@
         <v>8</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="J33" s="3">
         <v>0</v>
@@ -14008,12 +14024,12 @@
         <v>36</v>
       </c>
       <c r="R33" s="4" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="34" spans="1:18">
       <c r="A34" s="3" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D34" s="3">
         <v>6</v>
@@ -14022,10 +14038,10 @@
         <v>12</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J34" s="3">
         <v>0</v>
@@ -14037,12 +14053,12 @@
         <v>36</v>
       </c>
       <c r="R34" s="3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="35" spans="1:18">
       <c r="A35" s="4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D35" s="3">
         <v>8</v>
@@ -14051,10 +14067,10 @@
         <v>8</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="J35" s="3">
         <v>0</v>
@@ -14066,18 +14082,19 @@
         <v>36</v>
       </c>
       <c r="R35" s="4" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:R35"/>
   <hyperlinks>
     <hyperlink ref="P2" r:id="rId1"/>
-    <hyperlink ref="P3" r:id="rId2"/>
-    <hyperlink ref="P4" r:id="rId3"/>
-    <hyperlink ref="P5" r:id="rId4"/>
-    <hyperlink ref="P6" r:id="rId5"/>
-    <hyperlink ref="P7" r:id="rId6"/>
+    <hyperlink ref="Q2" r:id="rId2"/>
+    <hyperlink ref="P3" r:id="rId3"/>
+    <hyperlink ref="P4" r:id="rId4"/>
+    <hyperlink ref="P5" r:id="rId5"/>
+    <hyperlink ref="P6" r:id="rId6"/>
+    <hyperlink ref="P7" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -14155,19 +14172,19 @@
     </row>
     <row r="2" spans="1:18">
       <c r="A2" s="3" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="J2" s="3">
         <v>0</v>
@@ -14179,24 +14196,24 @@
         <v>36</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="4" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="J3" s="3">
         <v>0</v>
@@ -14208,24 +14225,24 @@
         <v>36</v>
       </c>
       <c r="R3" s="4" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="4" spans="1:18">
       <c r="A4" s="3" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="J4" s="3">
         <v>0</v>
@@ -14237,24 +14254,24 @@
         <v>36</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="5" spans="1:18">
       <c r="A5" s="4" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="J5" s="3">
         <v>0</v>
@@ -14266,24 +14283,24 @@
         <v>36</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="6" spans="1:18">
       <c r="A6" s="3" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="J6" s="3">
         <v>0</v>
@@ -14295,24 +14312,24 @@
         <v>36</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="7" spans="1:18">
       <c r="A7" s="4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="J7" s="3">
         <v>0</v>
@@ -14324,24 +14341,24 @@
         <v>36</v>
       </c>
       <c r="R7" s="4" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:18">
       <c r="A8" s="3" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="J8" s="3">
         <v>0</v>
@@ -14353,24 +14370,24 @@
         <v>36</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="4" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="J9" s="3">
         <v>0</v>
@@ -14382,24 +14399,24 @@
         <v>36</v>
       </c>
       <c r="R9" s="4" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="3" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="J10" s="3">
         <v>0</v>
@@ -14411,24 +14428,24 @@
         <v>36</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="11" spans="1:18">
       <c r="A11" s="4" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="J11" s="3">
         <v>0</v>
@@ -14440,24 +14457,24 @@
         <v>36</v>
       </c>
       <c r="R11" s="4" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="12" spans="1:18">
       <c r="A12" s="3" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="J12" s="3">
         <v>0</v>
@@ -14469,24 +14486,24 @@
         <v>36</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="4" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="J13" s="3">
         <v>0</v>
@@ -14498,24 +14515,24 @@
         <v>36</v>
       </c>
       <c r="R13" s="4" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="3" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="J14" s="3">
         <v>0</v>
@@ -14527,24 +14544,24 @@
         <v>36</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="15" spans="1:18">
       <c r="A15" s="4" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="J15" s="3">
         <v>0</v>
@@ -14556,24 +14573,24 @@
         <v>36</v>
       </c>
       <c r="R15" s="4" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="16" spans="1:18">
       <c r="A16" s="3" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="J16" s="3">
         <v>0</v>
@@ -14585,21 +14602,21 @@
         <v>36</v>
       </c>
       <c r="R16" s="3" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="17" spans="1:18">
       <c r="A17" s="4" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="J17" s="3">
         <v>0</v>
@@ -14608,27 +14625,27 @@
         <v>0</v>
       </c>
       <c r="O17" s="4" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="R17" s="4" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="18" spans="1:18">
       <c r="A18" s="3" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="J18" s="3">
         <v>0</v>
@@ -14640,24 +14657,24 @@
         <v>36</v>
       </c>
       <c r="R18" s="3" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="19" spans="1:18">
       <c r="A19" s="4" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="J19" s="3">
         <v>0</v>
@@ -14669,24 +14686,24 @@
         <v>36</v>
       </c>
       <c r="R19" s="4" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="20" spans="1:18">
       <c r="A20" s="3" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="J20" s="3">
         <v>0</v>
@@ -14698,24 +14715,24 @@
         <v>36</v>
       </c>
       <c r="R20" s="3" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="21" spans="1:18">
       <c r="A21" s="4" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="J21" s="3">
         <v>0</v>
@@ -14727,24 +14744,24 @@
         <v>36</v>
       </c>
       <c r="R21" s="4" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="22" spans="1:18">
       <c r="A22" s="3" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="J22" s="3">
         <v>0</v>
@@ -14756,24 +14773,24 @@
         <v>36</v>
       </c>
       <c r="R22" s="3" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="23" spans="1:18">
       <c r="A23" s="4" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="J23" s="3">
         <v>0</v>
@@ -14785,24 +14802,24 @@
         <v>36</v>
       </c>
       <c r="R23" s="4" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="24" spans="1:18">
       <c r="A24" s="3" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="J24" s="3">
         <v>0</v>
@@ -14814,24 +14831,24 @@
         <v>36</v>
       </c>
       <c r="R24" s="3" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="25" spans="1:18">
       <c r="A25" s="4" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="J25" s="3">
         <v>0</v>
@@ -14843,24 +14860,24 @@
         <v>36</v>
       </c>
       <c r="R25" s="4" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="26" spans="1:18">
       <c r="A26" s="3" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="J26" s="3">
         <v>0</v>
@@ -14872,24 +14889,24 @@
         <v>36</v>
       </c>
       <c r="R26" s="3" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="27" spans="1:18">
       <c r="A27" s="4" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="J27" s="3">
         <v>0</v>
@@ -14901,24 +14918,24 @@
         <v>36</v>
       </c>
       <c r="R27" s="4" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="28" spans="1:18">
       <c r="A28" s="3" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="J28" s="3">
         <v>0</v>
@@ -14930,24 +14947,24 @@
         <v>36</v>
       </c>
       <c r="R28" s="3" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="29" spans="1:18">
       <c r="A29" s="4" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="J29" s="3">
         <v>0</v>
@@ -14959,24 +14976,24 @@
         <v>36</v>
       </c>
       <c r="R29" s="4" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="30" spans="1:18">
       <c r="A30" s="3" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="J30" s="3">
         <v>0</v>
@@ -14988,24 +15005,24 @@
         <v>36</v>
       </c>
       <c r="R30" s="3" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="31" spans="1:18">
       <c r="A31" s="4" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="J31" s="3">
         <v>0</v>
@@ -15017,24 +15034,24 @@
         <v>36</v>
       </c>
       <c r="R31" s="4" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="32" spans="1:18">
       <c r="A32" s="3" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="J32" s="3">
         <v>0</v>
@@ -15046,7 +15063,7 @@
         <v>36</v>
       </c>
       <c r="R32" s="3" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
   </sheetData>
@@ -15127,16 +15144,16 @@
     </row>
     <row r="2" spans="1:18">
       <c r="A2" s="3" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="G2" s="3">
         <v>600</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="J2" s="3">
         <v>0</v>
@@ -15145,24 +15162,24 @@
         <v>0</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="4" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="G3" s="3">
         <v>450</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="J3" s="3">
         <v>0</v>
@@ -15174,21 +15191,21 @@
         <v>36</v>
       </c>
       <c r="R3" s="4" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="4" spans="1:18">
       <c r="A4" s="3" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="G4" s="3">
         <v>550</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="J4" s="3">
         <v>0</v>
@@ -15200,21 +15217,21 @@
         <v>36</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="5" spans="1:18">
       <c r="A5" s="4" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="G5" s="3">
         <v>1000</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="J5" s="3">
         <v>0</v>
@@ -15226,21 +15243,21 @@
         <v>36</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="6" spans="1:18">
       <c r="A6" s="3" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="G6" s="3">
         <v>750</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="J6" s="3">
         <v>0</v>
@@ -15252,21 +15269,21 @@
         <v>36</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="7" spans="1:18">
       <c r="A7" s="4" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="G7" s="3">
         <v>850</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="J7" s="3">
         <v>0</v>
@@ -15278,21 +15295,21 @@
         <v>36</v>
       </c>
       <c r="R7" s="4" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="8" spans="1:18">
       <c r="A8" s="3" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="G8" s="3">
         <v>1000</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="J8" s="3">
         <v>0</v>
@@ -15304,21 +15321,21 @@
         <v>36</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="4" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="G9" s="3">
         <v>750</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="J9" s="3">
         <v>0</v>
@@ -15330,21 +15347,21 @@
         <v>36</v>
       </c>
       <c r="R9" s="4" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="3" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="G10" s="3">
         <v>850</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="J10" s="3">
         <v>0</v>
@@ -15356,21 +15373,21 @@
         <v>36</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="11" spans="1:18">
       <c r="A11" s="4" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="G11" s="3">
         <v>500</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="J11" s="3">
         <v>0</v>
@@ -15382,21 +15399,21 @@
         <v>36</v>
       </c>
       <c r="R11" s="4" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="12" spans="1:18">
       <c r="A12" s="3" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="G12" s="3">
         <v>1000</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="J12" s="3">
         <v>0</v>
@@ -15408,21 +15425,21 @@
         <v>36</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="4" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="G13" s="3">
         <v>600</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="J13" s="3">
         <v>0</v>
@@ -15434,21 +15451,21 @@
         <v>36</v>
       </c>
       <c r="R13" s="4" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="3" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="G14" s="3">
         <v>750</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="J14" s="3">
         <v>0</v>
@@ -15460,21 +15477,21 @@
         <v>36</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="15" spans="1:18">
       <c r="A15" s="4" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="G15" s="3">
         <v>850</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="J15" s="3">
         <v>0</v>
@@ -15486,21 +15503,21 @@
         <v>36</v>
       </c>
       <c r="R15" s="4" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="16" spans="1:18">
       <c r="A16" s="3" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="G16" s="3">
         <v>400</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="J16" s="3">
         <v>0</v>
@@ -15512,7 +15529,7 @@
         <v>36</v>
       </c>
       <c r="R16" s="3" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
   </sheetData>
@@ -15593,13 +15610,13 @@
     </row>
     <row r="2" spans="1:18">
       <c r="A2" s="3" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="J2" s="3">
         <v>0</v>
@@ -15608,24 +15625,24 @@
         <v>0</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="4" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="J3" s="3">
         <v>0</v>
@@ -15637,21 +15654,21 @@
         <v>36</v>
       </c>
       <c r="R3" s="4" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="4" spans="1:18">
       <c r="A4" s="3" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="J4" s="3">
         <v>0</v>
@@ -15663,21 +15680,21 @@
         <v>36</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="5" spans="1:18">
       <c r="A5" s="4" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="J5" s="3">
         <v>0</v>
@@ -15689,21 +15706,21 @@
         <v>36</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="6" spans="1:18">
       <c r="A6" s="3" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="J6" s="3">
         <v>0</v>
@@ -15715,21 +15732,21 @@
         <v>36</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="7" spans="1:18">
       <c r="A7" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="J7" s="3">
         <v>0</v>
@@ -15741,21 +15758,21 @@
         <v>36</v>
       </c>
       <c r="R7" s="4" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="8" spans="1:18">
       <c r="A8" s="3" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="J8" s="3">
         <v>0</v>
@@ -15767,21 +15784,21 @@
         <v>36</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="4" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="J9" s="3">
         <v>0</v>
@@ -15793,21 +15810,21 @@
         <v>36</v>
       </c>
       <c r="R9" s="4" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="3" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="J10" s="3">
         <v>0</v>
@@ -15819,21 +15836,21 @@
         <v>36</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="11" spans="1:18">
       <c r="A11" s="4" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="J11" s="3">
         <v>0</v>
@@ -15845,21 +15862,21 @@
         <v>36</v>
       </c>
       <c r="R11" s="4" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="12" spans="1:18">
       <c r="A12" s="3" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="J12" s="3">
         <v>0</v>
@@ -15871,21 +15888,21 @@
         <v>36</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="4" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="J13" s="3">
         <v>0</v>
@@ -15897,21 +15914,21 @@
         <v>36</v>
       </c>
       <c r="R13" s="4" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="3" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="J14" s="3">
         <v>0</v>
@@ -15923,21 +15940,21 @@
         <v>36</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="15" spans="1:18">
       <c r="A15" s="4" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="J15" s="3">
         <v>0</v>
@@ -15949,21 +15966,21 @@
         <v>36</v>
       </c>
       <c r="R15" s="4" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="16" spans="1:18">
       <c r="A16" s="3" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="J16" s="3">
         <v>0</v>
@@ -15975,21 +15992,21 @@
         <v>36</v>
       </c>
       <c r="R16" s="3" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="17" spans="1:18">
       <c r="A17" s="4" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="J17" s="3">
         <v>0</v>
@@ -16001,21 +16018,21 @@
         <v>36</v>
       </c>
       <c r="R17" s="4" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="18" spans="1:18">
       <c r="A18" s="3" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="J18" s="3">
         <v>0</v>
@@ -16027,21 +16044,21 @@
         <v>36</v>
       </c>
       <c r="R18" s="3" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="19" spans="1:18">
       <c r="A19" s="4" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="J19" s="3">
         <v>0</v>
@@ -16053,21 +16070,21 @@
         <v>36</v>
       </c>
       <c r="R19" s="4" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="20" spans="1:18">
       <c r="A20" s="3" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="J20" s="3">
         <v>0</v>
@@ -16079,7 +16096,7 @@
         <v>36</v>
       </c>
       <c r="R20" s="3" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
   </sheetData>
@@ -16160,13 +16177,13 @@
     </row>
     <row r="2" spans="1:18">
       <c r="A2" s="3" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>460</v>
+        <v>146</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="J2" s="3">
         <v>0</v>
@@ -16178,18 +16195,18 @@
         <v>36</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="4" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>460</v>
+        <v>146</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="J3" s="3">
         <v>0</v>
@@ -16201,18 +16218,18 @@
         <v>36</v>
       </c>
       <c r="R3" s="4" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="4" spans="1:18">
       <c r="A4" s="3" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>460</v>
+        <v>146</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="J4" s="3">
         <v>0</v>
@@ -16224,18 +16241,18 @@
         <v>36</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="5" spans="1:18">
       <c r="A5" s="4" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>460</v>
+        <v>146</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="J5" s="3">
         <v>0</v>
@@ -16247,18 +16264,18 @@
         <v>36</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="6" spans="1:18">
       <c r="A6" s="3" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>460</v>
+        <v>146</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="J6" s="3">
         <v>0</v>
@@ -16270,18 +16287,18 @@
         <v>36</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="7" spans="1:18">
       <c r="A7" s="4" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>460</v>
+        <v>146</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="J7" s="3">
         <v>0</v>
@@ -16293,18 +16310,18 @@
         <v>36</v>
       </c>
       <c r="R7" s="4" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="8" spans="1:18">
       <c r="A8" s="3" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>460</v>
+        <v>146</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="J8" s="3">
         <v>0</v>
@@ -16316,18 +16333,18 @@
         <v>36</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="4" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>460</v>
+        <v>146</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="J9" s="3">
         <v>0</v>
@@ -16339,18 +16356,18 @@
         <v>36</v>
       </c>
       <c r="R9" s="4" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="3" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>460</v>
+        <v>146</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="J10" s="3">
         <v>0</v>
@@ -16362,7 +16379,7 @@
         <v>36</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
   </sheetData>
@@ -16443,16 +16460,16 @@
     </row>
     <row r="2" spans="1:18">
       <c r="A2" s="3" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="G2" s="3">
         <v>1000</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="J2" s="3">
         <v>0</v>
@@ -16464,21 +16481,21 @@
         <v>36</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="4" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="G3" s="3">
         <v>250</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="J3" s="3">
         <v>0</v>
@@ -16490,21 +16507,21 @@
         <v>36</v>
       </c>
       <c r="R3" s="4" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="4" spans="1:18">
       <c r="A4" s="3" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="G4" s="3">
         <v>500</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="J4" s="3">
         <v>0</v>
@@ -16516,21 +16533,21 @@
         <v>36</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="5" spans="1:18">
       <c r="A5" s="4" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="G5" s="3">
         <v>240</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="J5" s="3">
         <v>0</v>
@@ -16542,21 +16559,21 @@
         <v>36</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="6" spans="1:18">
       <c r="A6" s="3" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="G6" s="3">
         <v>480</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="J6" s="3">
         <v>0</v>
@@ -16568,21 +16585,21 @@
         <v>36</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="7" spans="1:18">
       <c r="A7" s="4" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="G7" s="3">
         <v>960</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="J7" s="3">
         <v>0</v>
@@ -16594,21 +16611,21 @@
         <v>36</v>
       </c>
       <c r="R7" s="4" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="8" spans="1:18">
       <c r="A8" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="G8" s="3">
         <v>1000</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="J8" s="3">
         <v>0</v>
@@ -16620,21 +16637,21 @@
         <v>36</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="4" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="G9" s="3">
         <v>250</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="J9" s="3">
         <v>0</v>
@@ -16646,21 +16663,21 @@
         <v>36</v>
       </c>
       <c r="R9" s="4" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="3" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="G10" s="3">
         <v>500</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="J10" s="3">
         <v>0</v>
@@ -16672,21 +16689,21 @@
         <v>36</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="11" spans="1:18">
       <c r="A11" s="4" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="G11" s="3">
         <v>2000</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="J11" s="3">
         <v>0</v>
@@ -16698,21 +16715,21 @@
         <v>36</v>
       </c>
       <c r="R11" s="4" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="12" spans="1:18">
       <c r="A12" s="3" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="G12" s="3">
         <v>4000</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="J12" s="3">
         <v>0</v>
@@ -16724,7 +16741,7 @@
         <v>36</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
   </sheetData>

--- a/Configuration_Catalogue.xlsx
+++ b/Configuration_Catalogue.xlsx
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2933" uniqueCount="608">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2931" uniqueCount="608">
   <si>
     <t>HARDWARE LAB | CATALOGUE</t>
   </si>
@@ -325,175 +325,175 @@
     <t>Assets/GPU/EVGA_RTX_2080_Ti_XC_HYBRID_GAMING_11G-P4-2384-KR.jpg</t>
   </si>
   <si>
+    <t>Component/GPU/EVGA_RTX_2080_Ti_XC_HYBRID_GAMING_11G-P4-2384-KR.json</t>
+  </si>
+  <si>
+    <t>NVIDIA GeForce RTX 2060 SUPER</t>
+  </si>
+  <si>
+    <t>Component/GPU/NVIDIA_GeForce_RTX_2060_SUPER.json</t>
+  </si>
+  <si>
+    <t>NVIDIA GeForce RTX 2070</t>
+  </si>
+  <si>
+    <t>Component/GPU/NVIDIA_GeForce_RTX_2070.json</t>
+  </si>
+  <si>
+    <t>NVIDIA GeForce RTX 2070 SUPER</t>
+  </si>
+  <si>
+    <t>Component/GPU/NVIDIA_GeForce_RTX_2070_SUPER.json</t>
+  </si>
+  <si>
+    <t>NVIDIA GeForce RTX 2080</t>
+  </si>
+  <si>
+    <t>Component/GPU/NVIDIA_GeForce_RTX_2080.json</t>
+  </si>
+  <si>
+    <t>NVIDIA GeForce RTX 2080 SUPER</t>
+  </si>
+  <si>
+    <t>Component/GPU/NVIDIA_GeForce_RTX_2080_SUPER.json</t>
+  </si>
+  <si>
+    <t>NVIDIA GeForce RTX 2080 Ti</t>
+  </si>
+  <si>
+    <t>Component/GPU/NVIDIA_GeForce_RTX_2080_Ti.json</t>
+  </si>
+  <si>
+    <t>NVIDIA GeForce RTX 3060</t>
+  </si>
+  <si>
+    <t>Component/GPU/NVIDIA_GeForce_RTX_3060.json</t>
+  </si>
+  <si>
+    <t>NVIDIA GeForce RTX 3060 Ti</t>
+  </si>
+  <si>
+    <t>Component/GPU/NVIDIA_GeForce_RTX_3060_Ti.json</t>
+  </si>
+  <si>
+    <t>NVIDIA GeForce RTX 3070</t>
+  </si>
+  <si>
+    <t>Component/GPU/NVIDIA_GeForce_RTX_3070.json</t>
+  </si>
+  <si>
+    <t>NVIDIA GeForce RTX 3070 Ti</t>
+  </si>
+  <si>
+    <t>GPU 8 Go GDDR6X, bus 256 bits.</t>
+  </si>
+  <si>
+    <t>Component/GPU/NVIDIA_GeForce_RTX_3070_Ti.json</t>
+  </si>
+  <si>
+    <t>NVIDIA GeForce RTX 3080</t>
+  </si>
+  <si>
+    <t>GPU 10 Go GDDR6X, bus 320 bits.</t>
+  </si>
+  <si>
+    <t>Component/GPU/NVIDIA_GeForce_RTX_3080.json</t>
+  </si>
+  <si>
+    <t>NVIDIA GeForce RTX 3080 Ti</t>
+  </si>
+  <si>
+    <t>GPU 12 Go GDDR6X, bus 384 bits.</t>
+  </si>
+  <si>
+    <t>Component/GPU/NVIDIA_GeForce_RTX_3080_Ti.json</t>
+  </si>
+  <si>
+    <t>NVIDIA GeForce RTX 3090</t>
+  </si>
+  <si>
+    <t>GPU 24 Go GDDR6X, bus 384 bits.</t>
+  </si>
+  <si>
+    <t>Component/GPU/NVIDIA_GeForce_RTX_3090.json</t>
+  </si>
+  <si>
+    <t>NVIDIA GeForce RTX 3090 Ti</t>
+  </si>
+  <si>
+    <t>Component/GPU/NVIDIA_GeForce_RTX_3090_Ti.json</t>
+  </si>
+  <si>
+    <t>NVIDIA GeForce RTX 4060 Ti 16GB</t>
+  </si>
+  <si>
+    <t>Component/GPU/NVIDIA_GeForce_RTX_4060_Ti_16GB.json</t>
+  </si>
+  <si>
+    <t>NVIDIA GeForce RTX 4070</t>
+  </si>
+  <si>
+    <t>GPU 12 Go GDDR6X, bus 192 bits.</t>
+  </si>
+  <si>
+    <t>Component/GPU/NVIDIA_GeForce_RTX_4070.json</t>
+  </si>
+  <si>
+    <t>NVIDIA GeForce RTX 4070 SUPER</t>
+  </si>
+  <si>
+    <t>Component/GPU/NVIDIA_GeForce_RTX_4070_SUPER.json</t>
+  </si>
+  <si>
+    <t>NVIDIA GeForce RTX 4070 Ti</t>
+  </si>
+  <si>
+    <t>Component/GPU/NVIDIA_GeForce_RTX_4070_Ti.json</t>
+  </si>
+  <si>
+    <t>NVIDIA GeForce RTX 4070 Ti SUPER</t>
+  </si>
+  <si>
+    <t>GPU 16 Go GDDR6X, bus 256 bits.</t>
+  </si>
+  <si>
+    <t>Component/GPU/NVIDIA_GeForce_RTX_4070_Ti_SUPER.json</t>
+  </si>
+  <si>
+    <t>NVIDIA GeForce RTX 4080</t>
+  </si>
+  <si>
+    <t>Component/GPU/NVIDIA_GeForce_RTX_4080.json</t>
+  </si>
+  <si>
+    <t>NVIDIA GeForce RTX 4080 SUPER</t>
+  </si>
+  <si>
+    <t>Component/GPU/NVIDIA_GeForce_RTX_4080_SUPER.json</t>
+  </si>
+  <si>
+    <t>NVIDIA GeForce RTX 4090</t>
+  </si>
+  <si>
+    <t>Component/GPU/NVIDIA_GeForce_RTX_4090.json</t>
+  </si>
+  <si>
+    <t>AMD Ryzen 5 1600</t>
+  </si>
+  <si>
+    <t>DDR4</t>
+  </si>
+  <si>
+    <t>AM4</t>
+  </si>
+  <si>
+    <t>Processeur AMD Ryzen 5 1600 pour PC de bureau, architecture Zen (Summit Ridge, variante AE 14 nm). 6 cœurs physiques et 12 threads grâce au SMT. Jeu d'instructions x86-64, AES pour accélérer les opérations cryptographiques, AVX2 et FMA3 pour les calculs vectoriels, virtualisation matérielle AMD-V. Fréquences 3,2 GHz de base et jusqu'à 3,6 GHz en boost ; cache L3 16 Mo, TDP 65 W. Plateforme AM4 avec mémoire DDR4 double canal et PCIe 3.0. Requiert une carte graphique dédiée. Ne pas confondre avec la variante AF 12 nm. Technologies documentées : x86-64 (64 bits), SMT, AES, AVX2, FMA3, AMD-V (virtualisation), AMD SenseMI, XFR.</t>
+  </si>
+  <si>
+    <t>Assets/CPU/CPU - AMD Ryzen 5 1600.jpg</t>
+  </si>
+  <si>
     <t>Ouvrir sources</t>
-  </si>
-  <si>
-    <t>Component/GPU/EVGA_RTX_2080_Ti_XC_HYBRID_GAMING_11G-P4-2384-KR.json</t>
-  </si>
-  <si>
-    <t>NVIDIA GeForce RTX 2060 SUPER</t>
-  </si>
-  <si>
-    <t>Component/GPU/NVIDIA_GeForce_RTX_2060_SUPER.json</t>
-  </si>
-  <si>
-    <t>NVIDIA GeForce RTX 2070</t>
-  </si>
-  <si>
-    <t>Component/GPU/NVIDIA_GeForce_RTX_2070.json</t>
-  </si>
-  <si>
-    <t>NVIDIA GeForce RTX 2070 SUPER</t>
-  </si>
-  <si>
-    <t>Component/GPU/NVIDIA_GeForce_RTX_2070_SUPER.json</t>
-  </si>
-  <si>
-    <t>NVIDIA GeForce RTX 2080</t>
-  </si>
-  <si>
-    <t>Component/GPU/NVIDIA_GeForce_RTX_2080.json</t>
-  </si>
-  <si>
-    <t>NVIDIA GeForce RTX 2080 SUPER</t>
-  </si>
-  <si>
-    <t>Component/GPU/NVIDIA_GeForce_RTX_2080_SUPER.json</t>
-  </si>
-  <si>
-    <t>NVIDIA GeForce RTX 2080 Ti</t>
-  </si>
-  <si>
-    <t>Component/GPU/NVIDIA_GeForce_RTX_2080_Ti.json</t>
-  </si>
-  <si>
-    <t>NVIDIA GeForce RTX 3060</t>
-  </si>
-  <si>
-    <t>Component/GPU/NVIDIA_GeForce_RTX_3060.json</t>
-  </si>
-  <si>
-    <t>NVIDIA GeForce RTX 3060 Ti</t>
-  </si>
-  <si>
-    <t>Component/GPU/NVIDIA_GeForce_RTX_3060_Ti.json</t>
-  </si>
-  <si>
-    <t>NVIDIA GeForce RTX 3070</t>
-  </si>
-  <si>
-    <t>Component/GPU/NVIDIA_GeForce_RTX_3070.json</t>
-  </si>
-  <si>
-    <t>NVIDIA GeForce RTX 3070 Ti</t>
-  </si>
-  <si>
-    <t>GPU 8 Go GDDR6X, bus 256 bits.</t>
-  </si>
-  <si>
-    <t>Component/GPU/NVIDIA_GeForce_RTX_3070_Ti.json</t>
-  </si>
-  <si>
-    <t>NVIDIA GeForce RTX 3080</t>
-  </si>
-  <si>
-    <t>GPU 10 Go GDDR6X, bus 320 bits.</t>
-  </si>
-  <si>
-    <t>Component/GPU/NVIDIA_GeForce_RTX_3080.json</t>
-  </si>
-  <si>
-    <t>NVIDIA GeForce RTX 3080 Ti</t>
-  </si>
-  <si>
-    <t>GPU 12 Go GDDR6X, bus 384 bits.</t>
-  </si>
-  <si>
-    <t>Component/GPU/NVIDIA_GeForce_RTX_3080_Ti.json</t>
-  </si>
-  <si>
-    <t>NVIDIA GeForce RTX 3090</t>
-  </si>
-  <si>
-    <t>GPU 24 Go GDDR6X, bus 384 bits.</t>
-  </si>
-  <si>
-    <t>Component/GPU/NVIDIA_GeForce_RTX_3090.json</t>
-  </si>
-  <si>
-    <t>NVIDIA GeForce RTX 3090 Ti</t>
-  </si>
-  <si>
-    <t>Component/GPU/NVIDIA_GeForce_RTX_3090_Ti.json</t>
-  </si>
-  <si>
-    <t>NVIDIA GeForce RTX 4060 Ti 16GB</t>
-  </si>
-  <si>
-    <t>Component/GPU/NVIDIA_GeForce_RTX_4060_Ti_16GB.json</t>
-  </si>
-  <si>
-    <t>NVIDIA GeForce RTX 4070</t>
-  </si>
-  <si>
-    <t>GPU 12 Go GDDR6X, bus 192 bits.</t>
-  </si>
-  <si>
-    <t>Component/GPU/NVIDIA_GeForce_RTX_4070.json</t>
-  </si>
-  <si>
-    <t>NVIDIA GeForce RTX 4070 SUPER</t>
-  </si>
-  <si>
-    <t>Component/GPU/NVIDIA_GeForce_RTX_4070_SUPER.json</t>
-  </si>
-  <si>
-    <t>NVIDIA GeForce RTX 4070 Ti</t>
-  </si>
-  <si>
-    <t>Component/GPU/NVIDIA_GeForce_RTX_4070_Ti.json</t>
-  </si>
-  <si>
-    <t>NVIDIA GeForce RTX 4070 Ti SUPER</t>
-  </si>
-  <si>
-    <t>GPU 16 Go GDDR6X, bus 256 bits.</t>
-  </si>
-  <si>
-    <t>Component/GPU/NVIDIA_GeForce_RTX_4070_Ti_SUPER.json</t>
-  </si>
-  <si>
-    <t>NVIDIA GeForce RTX 4080</t>
-  </si>
-  <si>
-    <t>Component/GPU/NVIDIA_GeForce_RTX_4080.json</t>
-  </si>
-  <si>
-    <t>NVIDIA GeForce RTX 4080 SUPER</t>
-  </si>
-  <si>
-    <t>Component/GPU/NVIDIA_GeForce_RTX_4080_SUPER.json</t>
-  </si>
-  <si>
-    <t>NVIDIA GeForce RTX 4090</t>
-  </si>
-  <si>
-    <t>Component/GPU/NVIDIA_GeForce_RTX_4090.json</t>
-  </si>
-  <si>
-    <t>AMD Ryzen 5 1600</t>
-  </si>
-  <si>
-    <t>DDR4</t>
-  </si>
-  <si>
-    <t>AM4</t>
-  </si>
-  <si>
-    <t>Processeur AMD Ryzen 5 1600 pour PC de bureau, architecture Zen (Summit Ridge, variante AE 14 nm). 6 cœurs physiques et 12 threads grâce au SMT. Jeu d'instructions x86-64, AES pour accélérer les opérations cryptographiques, AVX2 et FMA3 pour les calculs vectoriels, virtualisation matérielle AMD-V. Fréquences 3,2 GHz de base et jusqu'à 3,6 GHz en boost ; cache L3 16 Mo, TDP 65 W. Plateforme AM4 avec mémoire DDR4 double canal et PCIe 3.0. Requiert une carte graphique dédiée. Ne pas confondre avec la variante AF 12 nm. Technologies documentées : x86-64 (64 bits), SMT, AES, AVX2, FMA3, AMD-V (virtualisation), AMD SenseMI, XFR.</t>
-  </si>
-  <si>
-    <t>Assets/CPU/CPU - AMD Ryzen 5 1600.jpg</t>
   </si>
   <si>
     <t>Component/CPU/AMD_Ryzen_5_1600.json</t>
@@ -3787,7 +3787,7 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B26" t="s">
         <v>3</v>
@@ -3802,7 +3802,7 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B27" t="s">
         <v>3</v>
@@ -3817,7 +3817,7 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B28" t="s">
         <v>3</v>
@@ -3832,7 +3832,7 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B29" t="s">
         <v>3</v>
@@ -3847,7 +3847,7 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B30" t="s">
         <v>3</v>
@@ -3862,7 +3862,7 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B31" t="s">
         <v>3</v>
@@ -3877,7 +3877,7 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B32" t="s">
         <v>3</v>
@@ -3892,7 +3892,7 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B33" t="s">
         <v>3</v>
@@ -3907,7 +3907,7 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B34" t="s">
         <v>3</v>
@@ -3922,7 +3922,7 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B35" t="s">
         <v>3</v>
@@ -3937,7 +3937,7 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B36" t="s">
         <v>3</v>
@@ -3952,7 +3952,7 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B37" t="s">
         <v>3</v>
@@ -3967,7 +3967,7 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B38" t="s">
         <v>3</v>
@@ -3982,7 +3982,7 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B39" t="s">
         <v>3</v>
@@ -3997,7 +3997,7 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B40" t="s">
         <v>3</v>
@@ -4012,7 +4012,7 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B41" t="s">
         <v>3</v>
@@ -4027,7 +4027,7 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B42" t="s">
         <v>3</v>
@@ -4042,7 +4042,7 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B43" t="s">
         <v>3</v>
@@ -4057,7 +4057,7 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B44" t="s">
         <v>3</v>
@@ -4072,7 +4072,7 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B45" t="s">
         <v>3</v>
@@ -4087,7 +4087,7 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B46" t="s">
         <v>3</v>
@@ -4102,7 +4102,7 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B47" t="s">
         <v>3</v>
@@ -4117,7 +4117,7 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B48" t="s">
         <v>4</v>
@@ -7045,11 +7045,8 @@
       <c r="Q25" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="R25" s="3" t="s">
+      <c r="S25" s="4" t="s">
         <v>93</v>
-      </c>
-      <c r="S25" s="4" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -7057,7 +7054,7 @@
         <v>3</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H26" s="3">
         <v>8</v>
@@ -7075,7 +7072,7 @@
         <v>36</v>
       </c>
       <c r="S26" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -7083,7 +7080,7 @@
         <v>3</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H27" s="3">
         <v>8</v>
@@ -7101,7 +7098,7 @@
         <v>36</v>
       </c>
       <c r="S27" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -7109,7 +7106,7 @@
         <v>3</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H28" s="3">
         <v>8</v>
@@ -7127,7 +7124,7 @@
         <v>36</v>
       </c>
       <c r="S28" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="29" spans="1:19">
@@ -7135,7 +7132,7 @@
         <v>3</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H29" s="3">
         <v>8</v>
@@ -7153,7 +7150,7 @@
         <v>36</v>
       </c>
       <c r="S29" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="30" spans="1:19">
@@ -7161,7 +7158,7 @@
         <v>3</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H30" s="3">
         <v>8</v>
@@ -7179,7 +7176,7 @@
         <v>36</v>
       </c>
       <c r="S30" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="31" spans="1:19">
@@ -7187,7 +7184,7 @@
         <v>3</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H31" s="3">
         <v>11</v>
@@ -7205,7 +7202,7 @@
         <v>36</v>
       </c>
       <c r="S31" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="32" spans="1:19">
@@ -7213,7 +7210,7 @@
         <v>3</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H32" s="3">
         <v>12</v>
@@ -7231,7 +7228,7 @@
         <v>36</v>
       </c>
       <c r="S32" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="33" spans="1:19">
@@ -7239,7 +7236,7 @@
         <v>3</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H33" s="3">
         <v>8</v>
@@ -7257,7 +7254,7 @@
         <v>36</v>
       </c>
       <c r="S33" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="34" spans="1:19">
@@ -7265,7 +7262,7 @@
         <v>3</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H34" s="3">
         <v>8</v>
@@ -7283,7 +7280,7 @@
         <v>36</v>
       </c>
       <c r="S34" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="35" spans="1:19">
@@ -7291,25 +7288,25 @@
         <v>3</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H35" s="3">
         <v>8</v>
       </c>
       <c r="I35" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="K35" s="3">
+        <v>0</v>
+      </c>
+      <c r="M35" s="3">
+        <v>0</v>
+      </c>
+      <c r="P35" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="S35" s="4" t="s">
         <v>114</v>
-      </c>
-      <c r="K35" s="3">
-        <v>0</v>
-      </c>
-      <c r="M35" s="3">
-        <v>0</v>
-      </c>
-      <c r="P35" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="S35" s="4" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="36" spans="1:19">
@@ -7317,25 +7314,25 @@
         <v>3</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H36" s="3">
         <v>10</v>
       </c>
       <c r="I36" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="K36" s="3">
+        <v>0</v>
+      </c>
+      <c r="M36" s="3">
+        <v>0</v>
+      </c>
+      <c r="P36" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="S36" s="3" t="s">
         <v>117</v>
-      </c>
-      <c r="K36" s="3">
-        <v>0</v>
-      </c>
-      <c r="M36" s="3">
-        <v>0</v>
-      </c>
-      <c r="P36" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="S36" s="3" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="37" spans="1:19">
@@ -7343,25 +7340,25 @@
         <v>3</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H37" s="3">
         <v>12</v>
       </c>
       <c r="I37" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="K37" s="3">
+        <v>0</v>
+      </c>
+      <c r="M37" s="3">
+        <v>0</v>
+      </c>
+      <c r="P37" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="S37" s="4" t="s">
         <v>120</v>
-      </c>
-      <c r="K37" s="3">
-        <v>0</v>
-      </c>
-      <c r="M37" s="3">
-        <v>0</v>
-      </c>
-      <c r="P37" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="S37" s="4" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="38" spans="1:19">
@@ -7369,25 +7366,25 @@
         <v>3</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H38" s="3">
         <v>24</v>
       </c>
       <c r="I38" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="K38" s="3">
+        <v>0</v>
+      </c>
+      <c r="M38" s="3">
+        <v>0</v>
+      </c>
+      <c r="P38" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="S38" s="3" t="s">
         <v>123</v>
-      </c>
-      <c r="K38" s="3">
-        <v>0</v>
-      </c>
-      <c r="M38" s="3">
-        <v>0</v>
-      </c>
-      <c r="P38" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="S38" s="3" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="39" spans="1:19">
@@ -7395,13 +7392,13 @@
         <v>3</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H39" s="3">
         <v>24</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K39" s="3">
         <v>0</v>
@@ -7413,7 +7410,7 @@
         <v>36</v>
       </c>
       <c r="S39" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="40" spans="1:19">
@@ -7421,7 +7418,7 @@
         <v>3</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H40" s="3">
         <v>16</v>
@@ -7439,7 +7436,7 @@
         <v>36</v>
       </c>
       <c r="S40" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="41" spans="1:19">
@@ -7447,25 +7444,25 @@
         <v>3</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H41" s="3">
         <v>12</v>
       </c>
       <c r="I41" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="K41" s="3">
+        <v>0</v>
+      </c>
+      <c r="M41" s="3">
+        <v>0</v>
+      </c>
+      <c r="P41" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="S41" s="4" t="s">
         <v>130</v>
-      </c>
-      <c r="K41" s="3">
-        <v>0</v>
-      </c>
-      <c r="M41" s="3">
-        <v>0</v>
-      </c>
-      <c r="P41" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="S41" s="4" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="42" spans="1:19">
@@ -7473,13 +7470,13 @@
         <v>3</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H42" s="3">
         <v>12</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -7491,7 +7488,7 @@
         <v>36</v>
       </c>
       <c r="S42" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="43" spans="1:19">
@@ -7499,13 +7496,13 @@
         <v>3</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H43" s="3">
         <v>12</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -7517,7 +7514,7 @@
         <v>36</v>
       </c>
       <c r="S43" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="44" spans="1:19">
@@ -7525,25 +7522,25 @@
         <v>3</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H44" s="3">
         <v>16</v>
       </c>
       <c r="I44" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="K44" s="3">
+        <v>0</v>
+      </c>
+      <c r="M44" s="3">
+        <v>0</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="S44" s="3" t="s">
         <v>137</v>
-      </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
-      <c r="M44" s="3">
-        <v>0</v>
-      </c>
-      <c r="P44" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="S44" s="3" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="45" spans="1:19">
@@ -7551,13 +7548,13 @@
         <v>3</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H45" s="3">
         <v>16</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -7569,7 +7566,7 @@
         <v>36</v>
       </c>
       <c r="S45" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="46" spans="1:19">
@@ -7577,13 +7574,13 @@
         <v>3</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H46" s="3">
         <v>16</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -7595,7 +7592,7 @@
         <v>36</v>
       </c>
       <c r="S46" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="47" spans="1:19">
@@ -7603,13 +7600,13 @@
         <v>3</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H47" s="3">
         <v>24</v>
       </c>
       <c r="I47" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -7621,7 +7618,7 @@
         <v>36</v>
       </c>
       <c r="S47" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="48" spans="1:19">
@@ -7629,10 +7626,10 @@
         <v>4</v>
       </c>
       <c r="B48" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="D48" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>146</v>
       </c>
       <c r="E48" s="3">
         <v>6</v>
@@ -7641,25 +7638,25 @@
         <v>12</v>
       </c>
       <c r="G48" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="I48" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="I48" s="3" t="s">
+      <c r="K48" s="3">
+        <v>0</v>
+      </c>
+      <c r="M48" s="3">
+        <v>0</v>
+      </c>
+      <c r="P48" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q48" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="K48" s="3">
-        <v>0</v>
-      </c>
-      <c r="M48" s="3">
-        <v>0</v>
-      </c>
-      <c r="P48" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q48" s="3" t="s">
+      <c r="R48" s="3" t="s">
         <v>149</v>
-      </c>
-      <c r="R48" s="3" t="s">
-        <v>93</v>
       </c>
       <c r="S48" s="3" t="s">
         <v>150</v>
@@ -7679,7 +7676,7 @@
         <v>12</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I49" s="4" t="s">
         <v>152</v>
@@ -7714,7 +7711,7 @@
         <v>12</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I50" s="3" t="s">
         <v>152</v>
@@ -7749,7 +7746,7 @@
         <v>12</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I51" s="4" t="s">
         <v>152</v>
@@ -7784,7 +7781,7 @@
         <v>12</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>152</v>
@@ -7886,7 +7883,7 @@
         <v>16</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I55" s="4" t="s">
         <v>171</v>
@@ -7918,7 +7915,7 @@
         <v>16</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I56" s="3" t="s">
         <v>171</v>
@@ -7950,7 +7947,7 @@
         <v>16</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I57" s="4" t="s">
         <v>171</v>
@@ -7982,7 +7979,7 @@
         <v>16</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I58" s="3" t="s">
         <v>171</v>
@@ -8014,7 +8011,7 @@
         <v>16</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I59" s="4" t="s">
         <v>171</v>
@@ -8046,7 +8043,7 @@
         <v>16</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I60" s="3" t="s">
         <v>171</v>
@@ -8174,7 +8171,7 @@
         <v>24</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I64" s="3" t="s">
         <v>192</v>
@@ -8206,7 +8203,7 @@
         <v>32</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I65" s="4" t="s">
         <v>195</v>
@@ -8750,7 +8747,7 @@
         <v>248</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I82" s="3" t="s">
         <v>249</v>
@@ -8782,7 +8779,7 @@
         <v>253</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I83" s="4" t="s">
         <v>254</v>
@@ -8878,7 +8875,7 @@
         <v>265</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I86" s="3" t="s">
         <v>266</v>
@@ -8942,7 +8939,7 @@
         <v>253</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I88" s="3" t="s">
         <v>273</v>
@@ -8974,7 +8971,7 @@
         <v>265</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I89" s="4" t="s">
         <v>276</v>
@@ -9038,7 +9035,7 @@
         <v>265</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I91" s="4" t="s">
         <v>283</v>
@@ -9134,7 +9131,7 @@
         <v>248</v>
       </c>
       <c r="G94" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I94" s="3" t="s">
         <v>292</v>
@@ -9227,7 +9224,7 @@
         <v>301</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I97" s="4" t="s">
         <v>302</v>
@@ -9259,7 +9256,7 @@
         <v>253</v>
       </c>
       <c r="G98" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I98" s="3" t="s">
         <v>305</v>
@@ -9291,7 +9288,7 @@
         <v>265</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I99" s="4" t="s">
         <v>308</v>
@@ -9323,7 +9320,7 @@
         <v>248</v>
       </c>
       <c r="G100" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I100" s="3" t="s">
         <v>311</v>
@@ -9355,7 +9352,7 @@
         <v>253</v>
       </c>
       <c r="G101" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I101" s="4" t="s">
         <v>314</v>
@@ -9387,7 +9384,7 @@
         <v>265</v>
       </c>
       <c r="G102" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I102" s="3" t="s">
         <v>317</v>
@@ -9515,7 +9512,7 @@
         <v>265</v>
       </c>
       <c r="G106" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I106" s="3" t="s">
         <v>329</v>
@@ -9547,7 +9544,7 @@
         <v>253</v>
       </c>
       <c r="G107" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I107" s="4" t="s">
         <v>332</v>
@@ -9579,7 +9576,7 @@
         <v>253</v>
       </c>
       <c r="G108" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I108" s="3" t="s">
         <v>335</v>
@@ -9611,7 +9608,7 @@
         <v>265</v>
       </c>
       <c r="G109" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I109" s="4" t="s">
         <v>338</v>
@@ -10716,7 +10713,7 @@
         <v>461</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I147" s="4" t="s">
         <v>462</v>
@@ -10742,7 +10739,7 @@
         <v>464</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I148" s="3" t="s">
         <v>465</v>
@@ -10768,7 +10765,7 @@
         <v>467</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I149" s="4" t="s">
         <v>468</v>
@@ -10794,7 +10791,7 @@
         <v>470</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I150" s="3" t="s">
         <v>471</v>
@@ -10820,7 +10817,7 @@
         <v>473</v>
       </c>
       <c r="D151" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I151" s="4" t="s">
         <v>474</v>
@@ -10846,7 +10843,7 @@
         <v>476</v>
       </c>
       <c r="D152" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I152" s="3" t="s">
         <v>477</v>
@@ -10872,7 +10869,7 @@
         <v>479</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I153" s="4" t="s">
         <v>480</v>
@@ -10898,7 +10895,7 @@
         <v>482</v>
       </c>
       <c r="D154" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I154" s="3" t="s">
         <v>483</v>
@@ -10924,7 +10921,7 @@
         <v>485</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I155" s="4" t="s">
         <v>486</v>
@@ -11849,14 +11846,13 @@
   </sheetData>
   <autoFilter ref="A1:S187"/>
   <hyperlinks>
-    <hyperlink ref="R25" r:id="rId1"/>
-    <hyperlink ref="Q48" r:id="rId2"/>
-    <hyperlink ref="R48" r:id="rId3"/>
-    <hyperlink ref="Q49" r:id="rId4"/>
-    <hyperlink ref="Q50" r:id="rId5"/>
-    <hyperlink ref="Q51" r:id="rId6"/>
-    <hyperlink ref="Q52" r:id="rId7"/>
-    <hyperlink ref="Q53" r:id="rId8"/>
+    <hyperlink ref="Q48" r:id="rId1"/>
+    <hyperlink ref="R48" r:id="rId2"/>
+    <hyperlink ref="Q49" r:id="rId3"/>
+    <hyperlink ref="Q50" r:id="rId4"/>
+    <hyperlink ref="Q51" r:id="rId5"/>
+    <hyperlink ref="Q52" r:id="rId6"/>
+    <hyperlink ref="Q53" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -12483,16 +12479,13 @@
       <c r="P25" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="Q25" s="3" t="s">
+      <c r="R25" s="4" t="s">
         <v>93</v>
-      </c>
-      <c r="R25" s="4" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="26" spans="1:18">
       <c r="A26" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G26" s="3">
         <v>8</v>
@@ -12510,12 +12503,12 @@
         <v>36</v>
       </c>
       <c r="R26" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="27" spans="1:18">
       <c r="A27" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G27" s="3">
         <v>8</v>
@@ -12533,12 +12526,12 @@
         <v>36</v>
       </c>
       <c r="R27" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="28" spans="1:18">
       <c r="A28" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G28" s="3">
         <v>8</v>
@@ -12556,12 +12549,12 @@
         <v>36</v>
       </c>
       <c r="R28" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="29" spans="1:18">
       <c r="A29" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G29" s="3">
         <v>8</v>
@@ -12579,12 +12572,12 @@
         <v>36</v>
       </c>
       <c r="R29" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="30" spans="1:18">
       <c r="A30" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G30" s="3">
         <v>8</v>
@@ -12602,12 +12595,12 @@
         <v>36</v>
       </c>
       <c r="R30" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="31" spans="1:18">
       <c r="A31" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G31" s="3">
         <v>11</v>
@@ -12625,12 +12618,12 @@
         <v>36</v>
       </c>
       <c r="R31" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="32" spans="1:18">
       <c r="A32" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G32" s="3">
         <v>12</v>
@@ -12648,12 +12641,12 @@
         <v>36</v>
       </c>
       <c r="R32" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="33" spans="1:18">
       <c r="A33" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G33" s="3">
         <v>8</v>
@@ -12671,12 +12664,12 @@
         <v>36</v>
       </c>
       <c r="R33" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="34" spans="1:18">
       <c r="A34" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G34" s="3">
         <v>8</v>
@@ -12694,110 +12687,110 @@
         <v>36</v>
       </c>
       <c r="R34" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="35" spans="1:18">
       <c r="A35" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G35" s="3">
         <v>8</v>
       </c>
       <c r="H35" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="J35" s="3">
+        <v>0</v>
+      </c>
+      <c r="L35" s="3">
+        <v>0</v>
+      </c>
+      <c r="O35" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="R35" s="4" t="s">
         <v>114</v>
-      </c>
-      <c r="J35" s="3">
-        <v>0</v>
-      </c>
-      <c r="L35" s="3">
-        <v>0</v>
-      </c>
-      <c r="O35" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="R35" s="4" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="36" spans="1:18">
       <c r="A36" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G36" s="3">
         <v>10</v>
       </c>
       <c r="H36" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="J36" s="3">
+        <v>0</v>
+      </c>
+      <c r="L36" s="3">
+        <v>0</v>
+      </c>
+      <c r="O36" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="R36" s="3" t="s">
         <v>117</v>
-      </c>
-      <c r="J36" s="3">
-        <v>0</v>
-      </c>
-      <c r="L36" s="3">
-        <v>0</v>
-      </c>
-      <c r="O36" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="R36" s="3" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="37" spans="1:18">
       <c r="A37" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G37" s="3">
         <v>12</v>
       </c>
       <c r="H37" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="J37" s="3">
+        <v>0</v>
+      </c>
+      <c r="L37" s="3">
+        <v>0</v>
+      </c>
+      <c r="O37" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="R37" s="4" t="s">
         <v>120</v>
-      </c>
-      <c r="J37" s="3">
-        <v>0</v>
-      </c>
-      <c r="L37" s="3">
-        <v>0</v>
-      </c>
-      <c r="O37" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="R37" s="4" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="38" spans="1:18">
       <c r="A38" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G38" s="3">
         <v>24</v>
       </c>
       <c r="H38" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="J38" s="3">
+        <v>0</v>
+      </c>
+      <c r="L38" s="3">
+        <v>0</v>
+      </c>
+      <c r="O38" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="R38" s="3" t="s">
         <v>123</v>
-      </c>
-      <c r="J38" s="3">
-        <v>0</v>
-      </c>
-      <c r="L38" s="3">
-        <v>0</v>
-      </c>
-      <c r="O38" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="R38" s="3" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="39" spans="1:18">
       <c r="A39" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G39" s="3">
         <v>24</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J39" s="3">
         <v>0</v>
@@ -12809,12 +12802,12 @@
         <v>36</v>
       </c>
       <c r="R39" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="40" spans="1:18">
       <c r="A40" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G40" s="3">
         <v>16</v>
@@ -12832,41 +12825,41 @@
         <v>36</v>
       </c>
       <c r="R40" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="41" spans="1:18">
       <c r="A41" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G41" s="3">
         <v>12</v>
       </c>
       <c r="H41" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="J41" s="3">
+        <v>0</v>
+      </c>
+      <c r="L41" s="3">
+        <v>0</v>
+      </c>
+      <c r="O41" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="R41" s="4" t="s">
         <v>130</v>
-      </c>
-      <c r="J41" s="3">
-        <v>0</v>
-      </c>
-      <c r="L41" s="3">
-        <v>0</v>
-      </c>
-      <c r="O41" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="R41" s="4" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="42" spans="1:18">
       <c r="A42" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G42" s="3">
         <v>12</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J42" s="3">
         <v>0</v>
@@ -12878,18 +12871,18 @@
         <v>36</v>
       </c>
       <c r="R42" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="43" spans="1:18">
       <c r="A43" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G43" s="3">
         <v>12</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J43" s="3">
         <v>0</v>
@@ -12901,41 +12894,41 @@
         <v>36</v>
       </c>
       <c r="R43" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="44" spans="1:18">
       <c r="A44" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G44" s="3">
         <v>16</v>
       </c>
       <c r="H44" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="J44" s="3">
+        <v>0</v>
+      </c>
+      <c r="L44" s="3">
+        <v>0</v>
+      </c>
+      <c r="O44" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="R44" s="3" t="s">
         <v>137</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
-      </c>
-      <c r="L44" s="3">
-        <v>0</v>
-      </c>
-      <c r="O44" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="R44" s="3" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="45" spans="1:18">
       <c r="A45" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G45" s="3">
         <v>16</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J45" s="3">
         <v>0</v>
@@ -12947,18 +12940,18 @@
         <v>36</v>
       </c>
       <c r="R45" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="46" spans="1:18">
       <c r="A46" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G46" s="3">
         <v>16</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J46" s="3">
         <v>0</v>
@@ -12970,18 +12963,18 @@
         <v>36</v>
       </c>
       <c r="R46" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="47" spans="1:18">
       <c r="A47" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G47" s="3">
         <v>24</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J47" s="3">
         <v>0</v>
@@ -12993,14 +12986,11 @@
         <v>36</v>
       </c>
       <c r="R47" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:R47"/>
-  <hyperlinks>
-    <hyperlink ref="Q25" r:id="rId1"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -13077,10 +13067,10 @@
     </row>
     <row r="2" spans="1:18">
       <c r="A2" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>146</v>
       </c>
       <c r="D2" s="3">
         <v>6</v>
@@ -13089,25 +13079,25 @@
         <v>12</v>
       </c>
       <c r="F2" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="J2" s="3">
+        <v>0</v>
+      </c>
+      <c r="L2" s="3">
+        <v>0</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="P2" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="J2" s="3">
-        <v>0</v>
-      </c>
-      <c r="L2" s="3">
-        <v>0</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="P2" s="3" t="s">
+      <c r="Q2" s="3" t="s">
         <v>149</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>93</v>
       </c>
       <c r="R2" s="3" t="s">
         <v>150</v>
@@ -13124,7 +13114,7 @@
         <v>12</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>152</v>
@@ -13156,7 +13146,7 @@
         <v>12</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>152</v>
@@ -13188,7 +13178,7 @@
         <v>12</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>152</v>
@@ -13220,7 +13210,7 @@
         <v>12</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>152</v>
@@ -13313,7 +13303,7 @@
         <v>16</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>171</v>
@@ -13342,7 +13332,7 @@
         <v>16</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>171</v>
@@ -13371,7 +13361,7 @@
         <v>16</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>171</v>
@@ -13400,7 +13390,7 @@
         <v>16</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>171</v>
@@ -13429,7 +13419,7 @@
         <v>16</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>171</v>
@@ -13458,7 +13448,7 @@
         <v>16</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>171</v>
@@ -13574,7 +13564,7 @@
         <v>24</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>192</v>
@@ -13603,7 +13593,7 @@
         <v>32</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H19" s="4" t="s">
         <v>195</v>
@@ -14181,7 +14171,7 @@
         <v>248</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>249</v>
@@ -14210,7 +14200,7 @@
         <v>253</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>254</v>
@@ -14297,7 +14287,7 @@
         <v>265</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>266</v>
@@ -14355,7 +14345,7 @@
         <v>253</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>273</v>
@@ -14384,7 +14374,7 @@
         <v>265</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>276</v>
@@ -14442,7 +14432,7 @@
         <v>265</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>283</v>
@@ -14529,7 +14519,7 @@
         <v>248</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>292</v>
@@ -14613,7 +14603,7 @@
         <v>301</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H17" s="4" t="s">
         <v>302</v>
@@ -14642,7 +14632,7 @@
         <v>253</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>305</v>
@@ -14671,7 +14661,7 @@
         <v>265</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H19" s="4" t="s">
         <v>308</v>
@@ -14700,7 +14690,7 @@
         <v>248</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>311</v>
@@ -14729,7 +14719,7 @@
         <v>253</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H21" s="4" t="s">
         <v>314</v>
@@ -14758,7 +14748,7 @@
         <v>265</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>317</v>
@@ -14874,7 +14864,7 @@
         <v>265</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>329</v>
@@ -14903,7 +14893,7 @@
         <v>253</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H27" s="4" t="s">
         <v>332</v>
@@ -14932,7 +14922,7 @@
         <v>253</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>335</v>
@@ -14961,7 +14951,7 @@
         <v>265</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H29" s="4" t="s">
         <v>338</v>
@@ -16180,7 +16170,7 @@
         <v>461</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>462</v>
@@ -16203,7 +16193,7 @@
         <v>464</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>465</v>
@@ -16226,7 +16216,7 @@
         <v>467</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>468</v>
@@ -16249,7 +16239,7 @@
         <v>470</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>471</v>
@@ -16272,7 +16262,7 @@
         <v>473</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>474</v>
@@ -16295,7 +16285,7 @@
         <v>476</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>477</v>
@@ -16318,7 +16308,7 @@
         <v>479</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>480</v>
@@ -16341,7 +16331,7 @@
         <v>482</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>483</v>
@@ -16364,7 +16354,7 @@
         <v>485</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>486</v>

--- a/Configuration_Catalogue.xlsx
+++ b/Configuration_Catalogue.xlsx
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2937" uniqueCount="610">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2939" uniqueCount="610">
   <si>
     <t>HARDWARE LAB | CATALOGUE</t>
   </si>
@@ -799,7 +799,7 @@
     <t>Mini-ITX</t>
   </si>
   <si>
-    <t>ASRock B550M-ITX/ac — Mini-ITX</t>
+    <t>Carte mère Mini-ITX au socket AM4, dotée du chipset AMD B550, destinée aux machines compactes. Un emplacement PCIe 4.0 x16 reçoit la carte graphique, tandis qu’un emplacement M.2 PCIe 4.0 x4/SATA et quatre ports SATA3 servent au stockage. Deux logements DDR4 assurent la mémoire système. Les sorties HDMI et DisplayPort sont disponibles avec un processeur doté d’un circuit graphique compatible. Réseau Realtek Gigabit, Wi-Fi 802.11ac, Bluetooth 4.2 et audio Realtek ALC887/897 7.1 canaux. Les prises en charge CPU dépendent de la version BIOS et de la liste de compatibilité ASRock.</t>
   </si>
   <si>
     <t>Component/Motherboard/ASRock_B550M-ITX_ac.json</t>
@@ -8776,6 +8776,9 @@
       <c r="P82" s="3" t="s">
         <v>36</v>
       </c>
+      <c r="R82" s="3" t="s">
+        <v>108</v>
+      </c>
       <c r="S82" s="3" t="s">
         <v>252</v>
       </c>
@@ -11870,6 +11873,7 @@
     <hyperlink ref="Q52" r:id="rId7"/>
     <hyperlink ref="R52" r:id="rId8"/>
     <hyperlink ref="Q53" r:id="rId9"/>
+    <hyperlink ref="R82" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -14215,6 +14219,9 @@
       <c r="O2" s="3" t="s">
         <v>36</v>
       </c>
+      <c r="Q2" s="3" t="s">
+        <v>108</v>
+      </c>
       <c r="R2" s="3" t="s">
         <v>252</v>
       </c>
@@ -15088,6 +15095,9 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:R32"/>
+  <hyperlinks>
+    <hyperlink ref="Q2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/Configuration_Catalogue.xlsx
+++ b/Configuration_Catalogue.xlsx
@@ -799,7 +799,7 @@
     <t>Mini-ITX</t>
   </si>
   <si>
-    <t>Carte mère Mini-ITX au socket AM4, dotée du chipset AMD B550, destinée aux machines compactes. Un emplacement PCIe 4.0 x16 reçoit la carte graphique, tandis qu’un emplacement M.2 PCIe 4.0 x4/SATA et quatre ports SATA3 servent au stockage. Deux logements DDR4 assurent la mémoire système. Les sorties HDMI et DisplayPort sont disponibles avec un processeur doté d’un circuit graphique compatible. Réseau Realtek Gigabit, Wi-Fi 802.11ac, Bluetooth 4.2 et audio Realtek ALC887/897 7.1 canaux. Les prises en charge CPU dépendent de la version BIOS et de la liste de compatibilité ASRock.</t>
+    <t>Carte mère Mini-ITX 170 × 170 mm à chipset AMD B550 et socket AM4. Elle permet de monter un PC compact Ryzen avec deux emplacements DDR4, une carte graphique PCIe x16, un SSD M.2 NVMe ou SATA et quatre disques SATA supplémentaires. Avec les Ryzen Vermeer/Matisse compatibles, le slot graphique et le M.2 peuvent fonctionner en PCIe 4.0 ; les APU utilisent selon génération des lignes PCIe 3.0. Réseau Gigabit Realtek, Wi-Fi 5 double bande et Bluetooth 4.2 sont intégrés. Les sorties HDMI et DisplayPort dépendent de la présence d'un GPU intégré dans le processeur. Audio HD Realtek 7.1, connectique USB Type-A et Type-C, surveillance et réglage des ventilateurs via UEFI. Pour une configuration, contrôler BIOS/CPU, hauteur du refroidissement, stockage disponible, alimentation et format de boîtier. Un seul port M.2 de stockage est prévu : l'emplacement M.2 Key E distinct sert au Wi-Fi.</t>
   </si>
   <si>
     <t>Component/Motherboard/ASRock_B550M-ITX_ac.json</t>
